--- a/files/Straight_Greyhound_upcoming_rated_prices.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices.xlsx
@@ -1100,30 +1100,33 @@
     <t xml:space="preserve">Jodi Davis</t>
   </si>
   <si>
-    <t xml:space="preserve">SASSY SIREN</t>
+    <t xml:space="preserve">FEDERAL SABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashley Bock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLATER'S GATOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUNA ROSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tammy Hancock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRET ASSASSIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brett Hazelgrove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOOKED ON HER</t>
   </si>
   <si>
     <t xml:space="preserve">Jamie Hosking</t>
   </si>
   <si>
-    <t xml:space="preserve">SLATER'S GATOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUNA ROSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tammy Hancock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECRET ASSASSIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brett Hazelgrove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOOKED ON HER</t>
-  </si>
-  <si>
     <t xml:space="preserve">MITTS WHITAKER</t>
   </si>
   <si>
@@ -1217,162 +1220,162 @@
     <t xml:space="preserve">2026-09-14T19:48:00</t>
   </si>
   <si>
-    <t xml:space="preserve">DO RUN BANDI</t>
+    <t xml:space="preserve">BIG OPERATOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHE'S BUBBLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVEN MORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Heilbronn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISSY MAYBELLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Clelland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALLY VISION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OH LENNY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARMOR DEFIANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lina Langmaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAABINGA TIGER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geoff Draheim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14T20:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAME OF LOVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANDO WHIRLWIND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keith Boan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUTA SUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPICY VIKING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barry Kitchener</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSUNAMI SEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anita Watts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOVING JESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIZZARO BOY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reg Hazelgrove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANAMA KING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14T20:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLDSTAR JOBLIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAST LOVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOAKI RADAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORLANDO BEACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chloe Muller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT'S AN ACE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Priest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOM GUMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZABDON JUSTICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFFLECK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14T20:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLIGHTS BOOKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gary Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASTON POSEIDON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mal Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUSTFUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANDO WATCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRETTY STRAIGHT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXHIBIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INLAND MARK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLDSTAR HECTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14T21:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT AIRLEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAPPING ACES</t>
   </si>
   <si>
     <t xml:space="preserve">Christopher Supple</t>
   </si>
   <si>
-    <t xml:space="preserve">BIG OPERATOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHE'S BUBBLES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVEN MORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Heilbronn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISSY MAYBELLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anne Clelland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SALLY VISION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARMOR DEFIANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lina Langmaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAABINGA TIGER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geoff Draheim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14T20:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAME OF LOVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANDO WHIRLWIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keith Boan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUTA SUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPICY VIKING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barry Kitchener</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSUNAMI SEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anita Watts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOVING JESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIZZARO BOY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reg Hazelgrove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANAMA KING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14T20:28:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOLDSTAR JOBLIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAST LOVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOAKI RADAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORLANDO BEACH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chloe Muller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT'S AN ACE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Priest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOM GUMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZABDON JUSTICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFFLECK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14T20:48:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLIGHTS BOOKED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gary Moore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASTON POSEIDON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mal Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUSTFUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANDO WATCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRETTY STRAIGHT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXHIBIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INLAND MARK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOLDSTAR HECTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14T21:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT AIRLEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YAPPING ACES</t>
-  </si>
-  <si>
     <t xml:space="preserve">GRANDIOSE GIRL</t>
   </si>
   <si>
@@ -1404,9 +1407,6 @@
   </si>
   <si>
     <t xml:space="preserve">BAREFOOT GYPSY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashley Bock</t>
   </si>
   <si>
     <t xml:space="preserve">RAYA'S ROMANCE</t>
@@ -19676,7 +19676,7 @@
         <v>41</v>
       </c>
       <c r="H165" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I165"/>
       <c r="J165" t="n">
@@ -19689,19 +19689,19 @@
         <v>359</v>
       </c>
       <c r="M165" t="n">
-        <v>3.66</v>
+        <v>3.25</v>
       </c>
       <c r="N165" t="n">
-        <v>3.17</v>
+        <v>2.93</v>
       </c>
       <c r="O165" t="n">
-        <v>5.64</v>
+        <v>5.02</v>
       </c>
       <c r="P165" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="Q165" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
@@ -19787,7 +19787,7 @@
         <v>41</v>
       </c>
       <c r="H166" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I166"/>
       <c r="J166" t="n">
@@ -19800,19 +19800,19 @@
         <v>361</v>
       </c>
       <c r="M166" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="N166" t="n">
-        <v>5.42</v>
+        <v>5.14</v>
       </c>
       <c r="O166" t="n">
-        <v>3.51</v>
+        <v>3.04</v>
       </c>
       <c r="P166" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q166" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
@@ -19898,7 +19898,7 @@
         <v>41</v>
       </c>
       <c r="H167" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I167"/>
       <c r="J167" t="n">
@@ -19911,73 +19911,73 @@
         <v>363</v>
       </c>
       <c r="M167" t="n">
-        <v>5.4</v>
+        <v>9.83</v>
       </c>
       <c r="N167" t="n">
-        <v>6.04</v>
+        <v>9.05</v>
       </c>
       <c r="O167" t="n">
-        <v>5.75</v>
+        <v>16.26</v>
       </c>
       <c r="P167" t="n">
-        <v>2.7</v>
+        <v>4.47</v>
       </c>
       <c r="Q167" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="R167" t="n">
-        <v>-0.4</v>
+        <v>-1.4</v>
       </c>
       <c r="S167" t="n">
-        <v>100.8</v>
+        <v>100.4</v>
       </c>
       <c r="T167" t="n">
-        <v>97.6</v>
+        <v>99.1</v>
       </c>
       <c r="U167" t="n">
-        <v>97.6</v>
+        <v>97.9</v>
       </c>
       <c r="V167" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="W167" t="n">
-        <v>101.1</v>
+        <v>98.2</v>
       </c>
       <c r="X167" t="n">
-        <v>98.2</v>
+        <v>96.3</v>
       </c>
       <c r="Y167" t="n">
-        <v>98.2</v>
+        <v>96.7</v>
       </c>
       <c r="Z167" t="n">
-        <v>97.6</v>
+        <v>99.1</v>
       </c>
       <c r="AA167" t="n">
-        <v>97.6</v>
+        <v>99.1</v>
       </c>
       <c r="AB167" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AC167" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AD167" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE167" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AF167" t="n">
         <v>2</v>
       </c>
       <c r="AG167" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AH167" t="n">
         <v>0</v>
       </c>
       <c r="AI167" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="AJ167" t="s">
         <v>46</v>
@@ -20009,7 +20009,7 @@
         <v>41</v>
       </c>
       <c r="H168" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I168"/>
       <c r="J168" t="n">
@@ -20022,22 +20022,22 @@
         <v>134</v>
       </c>
       <c r="M168" t="n">
-        <v>12.33</v>
+        <v>11.34</v>
       </c>
       <c r="N168" t="n">
-        <v>13.47</v>
+        <v>12.85</v>
       </c>
       <c r="O168" t="n">
-        <v>8.21</v>
+        <v>7.14</v>
       </c>
       <c r="P168" t="n">
-        <v>5.68</v>
+        <v>5.19</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.47</v>
+        <v>3.17</v>
       </c>
       <c r="R168" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="S168" t="n">
         <v>97.8</v>
@@ -20120,7 +20120,7 @@
         <v>41</v>
       </c>
       <c r="H169" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I169"/>
       <c r="J169" t="n">
@@ -20133,19 +20133,19 @@
         <v>366</v>
       </c>
       <c r="M169" t="n">
-        <v>12.54</v>
+        <v>11.65</v>
       </c>
       <c r="N169" t="n">
-        <v>10.78</v>
+        <v>10.25</v>
       </c>
       <c r="O169" t="n">
-        <v>13.93</v>
+        <v>12.55</v>
       </c>
       <c r="P169" t="n">
-        <v>5.68</v>
+        <v>5.24</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="R169" t="n">
         <v>-1.7</v>
@@ -20231,7 +20231,7 @@
         <v>41</v>
       </c>
       <c r="H170" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I170"/>
       <c r="J170" t="n">
@@ -20244,19 +20244,19 @@
         <v>368</v>
       </c>
       <c r="M170" t="n">
-        <v>17.32</v>
+        <v>16.07</v>
       </c>
       <c r="N170" t="n">
-        <v>14.08</v>
+        <v>13.31</v>
       </c>
       <c r="O170" t="n">
-        <v>18.39</v>
+        <v>16.59</v>
       </c>
       <c r="P170" t="n">
-        <v>7.71</v>
+        <v>7.14</v>
       </c>
       <c r="Q170" t="n">
-        <v>4.6</v>
+        <v>4.23</v>
       </c>
       <c r="R170" t="n">
         <v>-2.2</v>
@@ -20342,7 +20342,7 @@
         <v>41</v>
       </c>
       <c r="H171" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I171"/>
       <c r="J171" t="n">
@@ -20352,22 +20352,22 @@
         <v>369</v>
       </c>
       <c r="L171" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="M171" t="n">
-        <v>19.61</v>
+        <v>18.21</v>
       </c>
       <c r="N171" t="n">
-        <v>19.45</v>
+        <v>18.23</v>
       </c>
       <c r="O171" t="n">
-        <v>14.21</v>
+        <v>12.76</v>
       </c>
       <c r="P171" t="n">
-        <v>8.78</v>
+        <v>8.08</v>
       </c>
       <c r="Q171" t="n">
-        <v>5.16</v>
+        <v>4.74</v>
       </c>
       <c r="R171" t="n">
         <v>-2.2</v>
@@ -20453,35 +20453,35 @@
         <v>41</v>
       </c>
       <c r="H172" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I172"/>
       <c r="J172" t="n">
         <v>1</v>
       </c>
       <c r="K172" t="s">
+        <v>371</v>
+      </c>
+      <c r="L172" t="s">
         <v>370</v>
       </c>
-      <c r="L172" t="s">
-        <v>363</v>
-      </c>
       <c r="M172" t="n">
-        <v>24.37</v>
+        <v>22.55</v>
       </c>
       <c r="N172" t="n">
-        <v>22</v>
+        <v>20.92</v>
       </c>
       <c r="O172" t="n">
-        <v>21.93</v>
+        <v>19.28</v>
       </c>
       <c r="P172" t="n">
-        <v>10.88</v>
+        <v>9.97</v>
       </c>
       <c r="Q172" t="n">
-        <v>6.33</v>
+        <v>5.79</v>
       </c>
       <c r="R172" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="S172" t="n">
         <v>99.6</v>
@@ -20552,13 +20552,13 @@
         <v>3</v>
       </c>
       <c r="D173" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E173" t="n">
         <v>300</v>
       </c>
       <c r="F173" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G173" t="s">
         <v>41</v>
@@ -20571,10 +20571,10 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L173" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M173" t="n">
         <v>2.86</v>
@@ -20663,13 +20663,13 @@
         <v>3</v>
       </c>
       <c r="D174" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E174" t="n">
         <v>300</v>
       </c>
       <c r="F174" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G174" t="s">
         <v>41</v>
@@ -20682,7 +20682,7 @@
         <v>7</v>
       </c>
       <c r="K174" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L174" t="s">
         <v>134</v>
@@ -20774,13 +20774,13 @@
         <v>3</v>
       </c>
       <c r="D175" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E175" t="n">
         <v>300</v>
       </c>
       <c r="F175" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G175" t="s">
         <v>41</v>
@@ -20793,10 +20793,10 @@
         <v>4</v>
       </c>
       <c r="K175" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L175" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M175" t="n">
         <v>8.76</v>
@@ -20885,13 +20885,13 @@
         <v>3</v>
       </c>
       <c r="D176" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E176" t="n">
         <v>300</v>
       </c>
       <c r="F176" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G176" t="s">
         <v>41</v>
@@ -20904,10 +20904,10 @@
         <v>8</v>
       </c>
       <c r="K176" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L176" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M176" t="n">
         <v>9.64</v>
@@ -20996,13 +20996,13 @@
         <v>3</v>
       </c>
       <c r="D177" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E177" t="n">
         <v>300</v>
       </c>
       <c r="F177" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G177" t="s">
         <v>41</v>
@@ -21015,10 +21015,10 @@
         <v>1</v>
       </c>
       <c r="K177" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L177" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M177" t="n">
         <v>11.33</v>
@@ -21107,13 +21107,13 @@
         <v>3</v>
       </c>
       <c r="D178" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E178" t="n">
         <v>300</v>
       </c>
       <c r="F178" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G178" t="s">
         <v>41</v>
@@ -21126,7 +21126,7 @@
         <v>2</v>
       </c>
       <c r="K178" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L178" t="s">
         <v>123</v>
@@ -21218,13 +21218,13 @@
         <v>3</v>
       </c>
       <c r="D179" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E179" t="n">
         <v>300</v>
       </c>
       <c r="F179" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G179" t="s">
         <v>41</v>
@@ -21237,10 +21237,10 @@
         <v>6</v>
       </c>
       <c r="K179" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L179" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M179" t="n">
         <v>20.48</v>
@@ -21329,13 +21329,13 @@
         <v>3</v>
       </c>
       <c r="D180" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E180" t="n">
         <v>300</v>
       </c>
       <c r="F180" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G180" t="s">
         <v>41</v>
@@ -21348,10 +21348,10 @@
         <v>5</v>
       </c>
       <c r="K180" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L180" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M180" t="n">
         <v>43.84</v>
@@ -21440,13 +21440,13 @@
         <v>4</v>
       </c>
       <c r="D181" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E181" t="n">
         <v>300</v>
       </c>
       <c r="F181" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G181" t="s">
         <v>41</v>
@@ -21459,7 +21459,7 @@
         <v>1</v>
       </c>
       <c r="K181" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L181" t="s">
         <v>368</v>
@@ -21551,13 +21551,13 @@
         <v>4</v>
       </c>
       <c r="D182" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E182" t="n">
         <v>300</v>
       </c>
       <c r="F182" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G182" t="s">
         <v>41</v>
@@ -21570,10 +21570,10 @@
         <v>5</v>
       </c>
       <c r="K182" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L182" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M182" t="n">
         <v>3.12</v>
@@ -21662,13 +21662,13 @@
         <v>4</v>
       </c>
       <c r="D183" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E183" t="n">
         <v>300</v>
       </c>
       <c r="F183" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G183" t="s">
         <v>41</v>
@@ -21681,10 +21681,10 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L183" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M183" t="n">
         <v>8.77</v>
@@ -21767,13 +21767,13 @@
         <v>4</v>
       </c>
       <c r="D184" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E184" t="n">
         <v>300</v>
       </c>
       <c r="F184" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G184" t="s">
         <v>41</v>
@@ -21786,10 +21786,10 @@
         <v>7</v>
       </c>
       <c r="K184" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L184" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M184" t="n">
         <v>14.59</v>
@@ -21878,13 +21878,13 @@
         <v>4</v>
       </c>
       <c r="D185" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E185" t="n">
         <v>300</v>
       </c>
       <c r="F185" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G185" t="s">
         <v>41</v>
@@ -21897,10 +21897,10 @@
         <v>4</v>
       </c>
       <c r="K185" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L185" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M185" t="n">
         <v>16.98</v>
@@ -21989,13 +21989,13 @@
         <v>4</v>
       </c>
       <c r="D186" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E186" t="n">
         <v>300</v>
       </c>
       <c r="F186" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G186" t="s">
         <v>41</v>
@@ -22008,10 +22008,10 @@
         <v>8</v>
       </c>
       <c r="K186" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L186" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M186" t="n">
         <v>17.16</v>
@@ -22100,13 +22100,13 @@
         <v>4</v>
       </c>
       <c r="D187" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E187" t="n">
         <v>300</v>
       </c>
       <c r="F187" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G187" t="s">
         <v>41</v>
@@ -22119,7 +22119,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L187" t="s">
         <v>356</v>
@@ -22211,13 +22211,13 @@
         <v>4</v>
       </c>
       <c r="D188" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E188" t="n">
         <v>300</v>
       </c>
       <c r="F188" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G188" t="s">
         <v>41</v>
@@ -22230,10 +22230,10 @@
         <v>6</v>
       </c>
       <c r="K188" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L188" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M188" t="n">
         <v>56.38</v>
@@ -22322,7 +22322,7 @@
         <v>5</v>
       </c>
       <c r="D189" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E189" t="n">
         <v>300</v>
@@ -22338,76 +22338,76 @@
       </c>
       <c r="I189"/>
       <c r="J189" t="n">
+        <v>5</v>
+      </c>
+      <c r="K189" t="s">
+        <v>402</v>
+      </c>
+      <c r="L189" t="s">
+        <v>352</v>
+      </c>
+      <c r="M189" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N189" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="O189" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P189" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S189" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="T189" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="U189" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="V189" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="W189" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="X189" t="n">
+        <v>99.9</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF189" t="n">
         <v>3</v>
       </c>
-      <c r="K189" t="s">
-        <v>401</v>
-      </c>
-      <c r="L189" t="s">
-        <v>402</v>
-      </c>
-      <c r="M189" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N189" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="O189" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P189" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R189" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="S189" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="T189" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="U189" t="n">
-        <v>99.9</v>
-      </c>
-      <c r="V189" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="W189" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="X189" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="Y189" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="Z189" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="AA189" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="AB189" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC189" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD189" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE189" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF189" t="n">
-        <v>24</v>
-      </c>
       <c r="AG189" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AH189" t="n">
         <v>0</v>
@@ -22433,7 +22433,7 @@
         <v>5</v>
       </c>
       <c r="D190" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E190" t="n">
         <v>300</v>
@@ -22449,76 +22449,76 @@
       </c>
       <c r="I190"/>
       <c r="J190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K190" t="s">
         <v>403</v>
       </c>
       <c r="L190" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="M190" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="N190" t="n">
-        <v>4.76</v>
+        <v>3.42</v>
       </c>
       <c r="O190" t="n">
-        <v>4.71</v>
+        <v>4.58</v>
       </c>
       <c r="P190" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q190" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="R190" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="S190" t="n">
-        <v>99.8</v>
+        <v>100.8</v>
       </c>
       <c r="T190" t="n">
         <v>99.8</v>
       </c>
       <c r="U190" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="V190" t="n">
-        <v>103.9</v>
+        <v>102.9</v>
       </c>
       <c r="W190" t="n">
-        <v>101.1</v>
+        <v>100.5</v>
       </c>
       <c r="X190" t="n">
-        <v>99.9</v>
+        <v>99.6</v>
       </c>
       <c r="Y190" t="n">
-        <v>99.8</v>
+        <v>99.6</v>
       </c>
       <c r="Z190" t="n">
         <v>99.8</v>
       </c>
       <c r="AA190" t="n">
-        <v>103.6</v>
+        <v>102.4</v>
       </c>
       <c r="AB190" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC190" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AD190" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE190" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF190" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG190" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AH190" t="n">
         <v>0</v>
@@ -22544,7 +22544,7 @@
         <v>5</v>
       </c>
       <c r="D191" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E191" t="n">
         <v>300</v>
@@ -22560,73 +22560,73 @@
       </c>
       <c r="I191"/>
       <c r="J191" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K191" t="s">
         <v>404</v>
       </c>
       <c r="L191" t="s">
-        <v>366</v>
+        <v>405</v>
       </c>
       <c r="M191" t="n">
-        <v>4.84</v>
+        <v>5.18</v>
       </c>
       <c r="N191" t="n">
-        <v>4.35</v>
+        <v>6.81</v>
       </c>
       <c r="O191" t="n">
-        <v>7.6</v>
+        <v>6.85</v>
       </c>
       <c r="P191" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="Q191" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R191" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="S191" t="n">
-        <v>100.8</v>
+        <v>103.2</v>
       </c>
       <c r="T191" t="n">
-        <v>99.8</v>
+        <v>100.6</v>
       </c>
       <c r="U191" t="n">
-        <v>99.8</v>
+        <v>99.9</v>
       </c>
       <c r="V191" t="n">
-        <v>102.9</v>
+        <v>108.5</v>
       </c>
       <c r="W191" t="n">
-        <v>100.5</v>
+        <v>97.2</v>
       </c>
       <c r="X191" t="n">
-        <v>99.6</v>
+        <v>96.7</v>
       </c>
       <c r="Y191" t="n">
-        <v>99.6</v>
+        <v>96.8</v>
       </c>
       <c r="Z191" t="n">
-        <v>99.8</v>
+        <v>100.6</v>
       </c>
       <c r="AA191" t="n">
-        <v>102.4</v>
+        <v>100.6</v>
       </c>
       <c r="AB191" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE191" t="n">
         <v>30</v>
       </c>
-      <c r="AC191" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD191" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE191" t="n">
-        <v>32</v>
-      </c>
       <c r="AF191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG191" t="n">
         <v>32</v>
@@ -22655,7 +22655,7 @@
         <v>5</v>
       </c>
       <c r="D192" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E192" t="n">
         <v>300</v>
@@ -22671,76 +22671,76 @@
       </c>
       <c r="I192"/>
       <c r="J192" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K192" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L192" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M192" t="n">
-        <v>6.47</v>
+        <v>10.3</v>
       </c>
       <c r="N192" t="n">
-        <v>8.57</v>
+        <v>7.68</v>
       </c>
       <c r="O192" t="n">
-        <v>11.53</v>
+        <v>15.45</v>
       </c>
       <c r="P192" t="n">
-        <v>3.11</v>
+        <v>4.75</v>
       </c>
       <c r="Q192" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="R192" t="n">
-        <v>-0.5</v>
+        <v>-1.8</v>
       </c>
       <c r="S192" t="n">
-        <v>103.2</v>
+        <v>96.5</v>
       </c>
       <c r="T192" t="n">
-        <v>100.6</v>
+        <v>96.8</v>
       </c>
       <c r="U192" t="n">
-        <v>99.9</v>
+        <v>96.8</v>
       </c>
       <c r="V192" t="n">
-        <v>108.5</v>
+        <v>105.2</v>
       </c>
       <c r="W192" t="n">
-        <v>97.2</v>
+        <v>100.5</v>
       </c>
       <c r="X192" t="n">
-        <v>96.7</v>
+        <v>97.6</v>
       </c>
       <c r="Y192" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="Z192" t="n">
         <v>96.8</v>
       </c>
-      <c r="Z192" t="n">
-        <v>100.6</v>
-      </c>
       <c r="AA192" t="n">
-        <v>100.6</v>
+        <v>98.9</v>
       </c>
       <c r="AB192" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AC192" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AD192" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE192" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AF192" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="AG192" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AH192" t="n">
         <v>0</v>
@@ -22766,7 +22766,7 @@
         <v>5</v>
       </c>
       <c r="D193" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E193" t="n">
         <v>300</v>
@@ -22782,76 +22782,76 @@
       </c>
       <c r="I193"/>
       <c r="J193" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K193" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L193" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M193" t="n">
-        <v>12.66</v>
+        <v>14.43</v>
       </c>
       <c r="N193" t="n">
-        <v>9.65</v>
+        <v>15.32</v>
       </c>
       <c r="O193" t="n">
-        <v>25.31</v>
+        <v>12.57</v>
       </c>
       <c r="P193" t="n">
-        <v>5.83</v>
+        <v>6.42</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="R193" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="S193" t="n">
-        <v>96.5</v>
+        <v>86.7</v>
       </c>
       <c r="T193" t="n">
-        <v>96.8</v>
+        <v>97.3</v>
       </c>
       <c r="U193" t="n">
-        <v>96.8</v>
+        <v>95.9</v>
       </c>
       <c r="V193" t="n">
-        <v>105.2</v>
+        <v>106</v>
       </c>
       <c r="W193" t="n">
-        <v>100.5</v>
+        <v>99.5</v>
       </c>
       <c r="X193" t="n">
-        <v>97.6</v>
+        <v>95.2</v>
       </c>
       <c r="Y193" t="n">
-        <v>97.5</v>
+        <v>92.6</v>
       </c>
       <c r="Z193" t="n">
-        <v>96.8</v>
+        <v>95.9</v>
       </c>
       <c r="AA193" t="n">
-        <v>98.9</v>
+        <v>95.9</v>
       </c>
       <c r="AB193" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AC193" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AD193" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AE193" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AF193" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="AG193" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AH193" t="n">
         <v>0</v>
@@ -22877,7 +22877,7 @@
         <v>5</v>
       </c>
       <c r="D194" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E194" t="n">
         <v>300</v>
@@ -22893,76 +22893,76 @@
       </c>
       <c r="I194"/>
       <c r="J194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L194" t="s">
-        <v>410</v>
+        <v>352</v>
       </c>
       <c r="M194" t="n">
-        <v>16.98</v>
+        <v>20.86</v>
       </c>
       <c r="N194" t="n">
-        <v>18.55</v>
+        <v>22.53</v>
       </c>
       <c r="O194" t="n">
-        <v>19.96</v>
+        <v>10.69</v>
       </c>
       <c r="P194" t="n">
-        <v>7.74</v>
+        <v>9.23</v>
       </c>
       <c r="Q194" t="n">
-        <v>4.57</v>
+        <v>5.26</v>
       </c>
       <c r="R194" t="n">
-        <v>-1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="S194" t="n">
-        <v>86.7</v>
+        <v>89.9</v>
       </c>
       <c r="T194" t="n">
-        <v>97.3</v>
+        <v>91</v>
       </c>
       <c r="U194" t="n">
-        <v>95.9</v>
+        <v>94.9</v>
       </c>
       <c r="V194" t="n">
-        <v>106</v>
+        <v>104.1</v>
       </c>
       <c r="W194" t="n">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="X194" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="Y194" t="n">
         <v>95.2</v>
       </c>
-      <c r="Y194" t="n">
-        <v>92.6</v>
-      </c>
       <c r="Z194" t="n">
-        <v>95.9</v>
+        <v>91</v>
       </c>
       <c r="AA194" t="n">
-        <v>95.9</v>
+        <v>101</v>
       </c>
       <c r="AB194" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC194" t="n">
         <v>9</v>
       </c>
-      <c r="AC194" t="n">
-        <v>3</v>
-      </c>
       <c r="AD194" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE194" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF194" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AH194" t="n">
         <v>0</v>
@@ -22988,7 +22988,7 @@
         <v>5</v>
       </c>
       <c r="D195" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E195" t="n">
         <v>300</v>
@@ -23013,22 +23013,22 @@
         <v>412</v>
       </c>
       <c r="M195" t="n">
-        <v>60.12</v>
+        <v>50.07</v>
       </c>
       <c r="N195" t="n">
-        <v>50.28</v>
+        <v>40.47</v>
       </c>
       <c r="O195" t="n">
-        <v>117.68</v>
+        <v>73.5</v>
       </c>
       <c r="P195" t="n">
-        <v>26.49</v>
+        <v>21.54</v>
       </c>
       <c r="Q195" t="n">
-        <v>14.81</v>
+        <v>11.78</v>
       </c>
       <c r="R195" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="S195" t="n">
         <v>94.2</v>
@@ -23099,7 +23099,7 @@
         <v>5</v>
       </c>
       <c r="D196" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E196" t="n">
         <v>300</v>
@@ -23124,22 +23124,22 @@
         <v>414</v>
       </c>
       <c r="M196" t="n">
-        <v>71.54</v>
+        <v>59.21</v>
       </c>
       <c r="N196" t="n">
-        <v>57.91</v>
+        <v>46.58</v>
       </c>
       <c r="O196" t="n">
-        <v>70.82</v>
+        <v>43.94</v>
       </c>
       <c r="P196" t="n">
-        <v>31.91</v>
+        <v>26.17</v>
       </c>
       <c r="Q196" t="n">
-        <v>18.01</v>
+        <v>14.37</v>
       </c>
       <c r="R196" t="n">
-        <v>-4</v>
+        <v>-4.1</v>
       </c>
       <c r="S196" t="n">
         <v>95.5</v>
@@ -23232,7 +23232,7 @@
         <v>416</v>
       </c>
       <c r="L197" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M197" t="n">
         <v>3.2</v>
@@ -24003,7 +24003,7 @@
         <v>427</v>
       </c>
       <c r="L204" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M204" t="n">
         <v>29.4</v>
@@ -24114,7 +24114,7 @@
         <v>429</v>
       </c>
       <c r="L205" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M205" t="n">
         <v>2.56</v>
@@ -24219,7 +24219,7 @@
         <v>430</v>
       </c>
       <c r="L206" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M206" t="n">
         <v>5.3</v>
@@ -25440,7 +25440,7 @@
         <v>446</v>
       </c>
       <c r="L217" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M217" t="n">
         <v>27.79</v>
@@ -25767,7 +25767,7 @@
         <v>449</v>
       </c>
       <c r="L220" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M220" t="n">
         <v>109.67</v>
@@ -25878,7 +25878,7 @@
         <v>451</v>
       </c>
       <c r="L221" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="M221" t="n">
         <v>2.15</v>
@@ -25983,7 +25983,7 @@
         <v>452</v>
       </c>
       <c r="L222" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
       <c r="M222" t="n">
         <v>4.51</v>
@@ -26091,7 +26091,7 @@
         <v>2</v>
       </c>
       <c r="K223" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L223" t="s">
         <v>426</v>
@@ -26196,10 +26196,10 @@
         <v>5</v>
       </c>
       <c r="K224" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L224" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M224" t="n">
         <v>11.44</v>
@@ -26307,7 +26307,7 @@
         <v>8</v>
       </c>
       <c r="K225" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L225" t="s">
         <v>433</v>
@@ -26418,10 +26418,10 @@
         <v>6</v>
       </c>
       <c r="K226" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L226" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M226" t="n">
         <v>25.93</v>
@@ -26527,10 +26527,10 @@
         <v>4</v>
       </c>
       <c r="K227" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L227" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M227" t="n">
         <v>72.99</v>
@@ -26638,7 +26638,7 @@
         <v>7</v>
       </c>
       <c r="K228" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L228" t="s">
         <v>421</v>
@@ -26730,7 +26730,7 @@
         <v>10</v>
       </c>
       <c r="D229" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E229" t="n">
         <v>300</v>
@@ -26749,10 +26749,10 @@
         <v>7</v>
       </c>
       <c r="K229" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L229" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M229" t="n">
         <v>2.55</v>
@@ -26841,7 +26841,7 @@
         <v>10</v>
       </c>
       <c r="D230" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E230" t="n">
         <v>300</v>
@@ -26860,10 +26860,10 @@
         <v>4</v>
       </c>
       <c r="K230" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L230" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M230" t="n">
         <v>8.1</v>
@@ -26952,7 +26952,7 @@
         <v>10</v>
       </c>
       <c r="D231" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E231" t="n">
         <v>300</v>
@@ -26971,10 +26971,10 @@
         <v>5</v>
       </c>
       <c r="K231" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L231" t="s">
-        <v>464</v>
+        <v>363</v>
       </c>
       <c r="M231" t="n">
         <v>8.12</v>
@@ -27063,7 +27063,7 @@
         <v>10</v>
       </c>
       <c r="D232" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E232" t="n">
         <v>300</v>
@@ -27174,7 +27174,7 @@
         <v>10</v>
       </c>
       <c r="D233" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E233" t="n">
         <v>300</v>
@@ -27285,7 +27285,7 @@
         <v>10</v>
       </c>
       <c r="D234" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E234" t="n">
         <v>300</v>
@@ -27307,7 +27307,7 @@
         <v>468</v>
       </c>
       <c r="L234" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
       <c r="M234" t="n">
         <v>13.43</v>
@@ -27396,7 +27396,7 @@
         <v>10</v>
       </c>
       <c r="D235" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E235" t="n">
         <v>300</v>
@@ -27418,7 +27418,7 @@
         <v>469</v>
       </c>
       <c r="L235" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M235" t="n">
         <v>26.08</v>
@@ -27507,7 +27507,7 @@
         <v>10</v>
       </c>
       <c r="D236" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E236" t="n">
         <v>300</v>
@@ -27529,7 +27529,7 @@
         <v>470</v>
       </c>
       <c r="L236" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M236" t="n">
         <v>51.65</v>
@@ -27961,7 +27961,7 @@
         <v>475</v>
       </c>
       <c r="L240" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M240" t="n">
         <v>9.37</v>
@@ -28183,7 +28183,7 @@
         <v>477</v>
       </c>
       <c r="L242" t="s">
-        <v>464</v>
+        <v>363</v>
       </c>
       <c r="M242" t="n">
         <v>11.62</v>
@@ -28294,7 +28294,7 @@
         <v>478</v>
       </c>
       <c r="L243" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M243" t="n">
         <v>18.69</v>
@@ -28607,7 +28607,7 @@
         <v>483</v>
       </c>
       <c r="L246" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M246" t="n">
         <v>4.71</v>
@@ -28829,7 +28829,7 @@
         <v>485</v>
       </c>
       <c r="L248" t="s">
-        <v>464</v>
+        <v>363</v>
       </c>
       <c r="M248" t="n">
         <v>7.85</v>
@@ -29051,7 +29051,7 @@
         <v>487</v>
       </c>
       <c r="L250" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
       <c r="M250" t="n">
         <v>13.26</v>
@@ -29162,7 +29162,7 @@
         <v>488</v>
       </c>
       <c r="L251" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M251" t="n">
         <v>30.33</v>

--- a/files/Straight_Greyhound_upcoming_rated_prices.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices.xlsx
@@ -488,13 +488,13 @@
     <t xml:space="preserve">KING OF ASGARD</t>
   </si>
   <si>
+    <t xml:space="preserve">COOL GENT</t>
+  </si>
+  <si>
     <t xml:space="preserve">HARA'S USAIN</t>
   </si>
   <si>
     <t xml:space="preserve">Peter Carleton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COOL GENT</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-20T14:47:00</t>
@@ -2037,16 +2037,16 @@
         <v>44</v>
       </c>
       <c r="M2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="N2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O2" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="P2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Q2" t="n">
         <v>1.03</v>
@@ -2146,14 +2146,14 @@
         <v>48</v>
       </c>
       <c r="M3" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="N3"/>
       <c r="O3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="P3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.05</v>
@@ -2239,16 +2239,16 @@
         <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>12.23</v>
+        <v>12.16</v>
       </c>
       <c r="N4" t="n">
-        <v>14.92</v>
+        <v>14.84</v>
       </c>
       <c r="O4" t="n">
-        <v>10.41</v>
+        <v>10.33</v>
       </c>
       <c r="P4" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="Q4" t="n">
         <v>1.31</v>
@@ -2350,16 +2350,16 @@
         <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>28.22</v>
+        <v>28.16</v>
       </c>
       <c r="N5" t="n">
-        <v>35.63</v>
+        <v>35.5</v>
       </c>
       <c r="O5" t="n">
-        <v>29.03</v>
+        <v>28.88</v>
       </c>
       <c r="P5" t="n">
-        <v>9.79</v>
+        <v>9.76</v>
       </c>
       <c r="Q5" t="n">
         <v>3.15</v>
@@ -2459,14 +2459,14 @@
         <v>56</v>
       </c>
       <c r="M6" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="N6"/>
       <c r="O6" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
         <v>1.36</v>
@@ -2552,7 +2552,7 @@
         <v>58</v>
       </c>
       <c r="M7" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="N7"/>
       <c r="O7" t="n">
@@ -2645,11 +2645,11 @@
         <v>60</v>
       </c>
       <c r="M8" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="N8"/>
       <c r="O8" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="P8" t="n">
         <v>2.08</v>
@@ -2738,22 +2738,22 @@
         <v>62</v>
       </c>
       <c r="M9" t="n">
-        <v>7.25</v>
+        <v>7.29</v>
       </c>
       <c r="N9" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>8.68</v>
+        <v>8.75</v>
       </c>
       <c r="P9" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="S9" t="n">
         <v>98</v>
@@ -2849,16 +2849,16 @@
         <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>19.89</v>
+        <v>19.94</v>
       </c>
       <c r="N10" t="n">
-        <v>20.62</v>
+        <v>20.65</v>
       </c>
       <c r="O10" t="n">
-        <v>20.72</v>
+        <v>20.76</v>
       </c>
       <c r="P10" t="n">
-        <v>8.16</v>
+        <v>8.17</v>
       </c>
       <c r="Q10" t="n">
         <v>4.45</v>
@@ -2958,19 +2958,19 @@
         <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>50.59</v>
+        <v>50.39</v>
       </c>
       <c r="N11" t="n">
-        <v>49.29</v>
+        <v>49.1</v>
       </c>
       <c r="O11" t="n">
-        <v>113.17</v>
+        <v>112.65</v>
       </c>
       <c r="P11" t="n">
-        <v>20.28</v>
+        <v>20.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.24</v>
+        <v>10.19</v>
       </c>
       <c r="R11" t="n">
         <v>-4.2</v>
@@ -3069,19 +3069,19 @@
         <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>162.03</v>
+        <v>163.12</v>
       </c>
       <c r="N12" t="n">
-        <v>195.71</v>
+        <v>196.48</v>
       </c>
       <c r="O12" t="n">
-        <v>137.75</v>
+        <v>139.26</v>
       </c>
       <c r="P12" t="n">
-        <v>62.27</v>
+        <v>62.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>31.11</v>
+        <v>31.36</v>
       </c>
       <c r="R12" t="n">
         <v>-6</v>
@@ -3184,7 +3184,7 @@
         <v>1.64</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="P13" t="n">
         <v>1.25</v>
@@ -3287,16 +3287,16 @@
         <v>72</v>
       </c>
       <c r="M14" t="n">
-        <v>5.82</v>
+        <v>5.88</v>
       </c>
       <c r="N14" t="n">
-        <v>7.26</v>
+        <v>7.33</v>
       </c>
       <c r="O14" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q14" t="n">
         <v>1.46</v>
@@ -3404,7 +3404,7 @@
         <v>9.86</v>
       </c>
       <c r="O15" t="n">
-        <v>6.27</v>
+        <v>6.26</v>
       </c>
       <c r="P15" t="n">
         <v>2.52</v>
@@ -3509,19 +3509,19 @@
         <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>21.11</v>
+        <v>21.26</v>
       </c>
       <c r="N16" t="n">
-        <v>23.3</v>
+        <v>23.49</v>
       </c>
       <c r="O16" t="n">
-        <v>37.44</v>
+        <v>37.61</v>
       </c>
       <c r="P16" t="n">
-        <v>7.72</v>
+        <v>7.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="R16" t="n">
         <v>-3.1</v>
@@ -3620,16 +3620,16 @@
         <v>78</v>
       </c>
       <c r="M17" t="n">
-        <v>26.55</v>
+        <v>26.58</v>
       </c>
       <c r="N17" t="n">
-        <v>18.55</v>
+        <v>18.56</v>
       </c>
       <c r="O17" t="n">
-        <v>52.64</v>
+        <v>52.67</v>
       </c>
       <c r="P17" t="n">
-        <v>9.58</v>
+        <v>9.59</v>
       </c>
       <c r="Q17" t="n">
         <v>4.97</v>
@@ -3731,19 +3731,19 @@
         <v>80</v>
       </c>
       <c r="M18" t="n">
-        <v>37.34</v>
+        <v>37.04</v>
       </c>
       <c r="N18" t="n">
-        <v>38.87</v>
+        <v>38.57</v>
       </c>
       <c r="O18" t="n">
-        <v>79.76</v>
+        <v>79.09</v>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.39</v>
+        <v>6.33</v>
       </c>
       <c r="R18" t="n">
         <v>-3.9</v>
@@ -3842,19 +3842,19 @@
         <v>56</v>
       </c>
       <c r="M19" t="n">
-        <v>43.42</v>
+        <v>43.11</v>
       </c>
       <c r="N19" t="n">
-        <v>35.03</v>
+        <v>34.79</v>
       </c>
       <c r="O19" t="n">
-        <v>70.02</v>
+        <v>69.48</v>
       </c>
       <c r="P19" t="n">
-        <v>15.69</v>
+        <v>15.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.81</v>
+        <v>7.75</v>
       </c>
       <c r="R19" t="n">
         <v>-4.3</v>
@@ -3953,10 +3953,10 @@
         <v>85</v>
       </c>
       <c r="M20" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="O20" t="n">
         <v>1.77</v>
@@ -4064,16 +4064,16 @@
         <v>50</v>
       </c>
       <c r="M21" t="n">
-        <v>5.12</v>
+        <v>5.09</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>4.88</v>
       </c>
       <c r="O21" t="n">
-        <v>7.75</v>
+        <v>7.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
         <v>1.44</v>
@@ -4175,22 +4175,22 @@
         <v>88</v>
       </c>
       <c r="M22" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="O22" t="n">
-        <v>7.46</v>
+        <v>7.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="Q22" t="n">
         <v>1.59</v>
       </c>
       <c r="R22" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="S22" t="n">
         <v>101.1</v>
@@ -4284,16 +4284,16 @@
         <v>72</v>
       </c>
       <c r="M23" t="n">
-        <v>14.55</v>
+        <v>14.52</v>
       </c>
       <c r="N23" t="n">
-        <v>14.96</v>
+        <v>14.93</v>
       </c>
       <c r="O23" t="n">
-        <v>9.96</v>
+        <v>9.92</v>
       </c>
       <c r="P23" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="Q23" t="n">
         <v>3.35</v>
@@ -4393,19 +4393,19 @@
         <v>62</v>
       </c>
       <c r="M24" t="n">
-        <v>14.94</v>
+        <v>14.82</v>
       </c>
       <c r="N24" t="n">
-        <v>13.52</v>
+        <v>13.42</v>
       </c>
       <c r="O24" t="n">
-        <v>17.21</v>
+        <v>17.06</v>
       </c>
       <c r="P24" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
         <v>-2.8</v>
@@ -4504,19 +4504,19 @@
         <v>76</v>
       </c>
       <c r="M25" t="n">
-        <v>29.51</v>
+        <v>29.17</v>
       </c>
       <c r="N25" t="n">
-        <v>27.99</v>
+        <v>27.71</v>
       </c>
       <c r="O25" t="n">
-        <v>81.14</v>
+        <v>80.15</v>
       </c>
       <c r="P25" t="n">
-        <v>11.42</v>
+        <v>11.29</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.73</v>
+        <v>5.68</v>
       </c>
       <c r="R25" t="n">
         <v>-3.7</v>
@@ -4615,16 +4615,16 @@
         <v>97</v>
       </c>
       <c r="M26" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="N26" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="O26" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="P26" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
         <v>1.69</v>
@@ -4724,19 +4724,19 @@
         <v>100</v>
       </c>
       <c r="M27" t="n">
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="N27" t="n">
-        <v>5.76</v>
+        <v>5.81</v>
       </c>
       <c r="O27" t="n">
-        <v>5.61</v>
+        <v>5.66</v>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
         <v>-0.2</v>
@@ -4942,19 +4942,19 @@
         <v>100</v>
       </c>
       <c r="M29" t="n">
-        <v>8.58</v>
+        <v>8.59</v>
       </c>
       <c r="N29" t="n">
-        <v>8.12</v>
+        <v>8.13</v>
       </c>
       <c r="O29" t="n">
-        <v>8.88</v>
+        <v>8.9</v>
       </c>
       <c r="P29" t="n">
         <v>4.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
         <v>-1</v>
@@ -5051,19 +5051,19 @@
         <v>72</v>
       </c>
       <c r="M30" t="n">
-        <v>10.47</v>
+        <v>10.53</v>
       </c>
       <c r="N30" t="n">
-        <v>9.02</v>
+        <v>9.06</v>
       </c>
       <c r="O30" t="n">
-        <v>7.34</v>
+        <v>7.38</v>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
         <v>-1.4</v>
@@ -5160,19 +5160,19 @@
         <v>72</v>
       </c>
       <c r="M31" t="n">
-        <v>13.94</v>
+        <v>13.84</v>
       </c>
       <c r="N31" t="n">
-        <v>10.8</v>
+        <v>10.72</v>
       </c>
       <c r="O31" t="n">
-        <v>9.18</v>
+        <v>9.11</v>
       </c>
       <c r="P31" t="n">
-        <v>6.53</v>
+        <v>6.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="R31" t="n">
         <v>-1.9</v>
@@ -5269,19 +5269,19 @@
         <v>50</v>
       </c>
       <c r="M32" t="n">
-        <v>14.23</v>
+        <v>14.12</v>
       </c>
       <c r="N32" t="n">
-        <v>14.5</v>
+        <v>14.41</v>
       </c>
       <c r="O32" t="n">
-        <v>15.61</v>
+        <v>15.5</v>
       </c>
       <c r="P32" t="n">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="R32" t="n">
         <v>-1.7</v>
@@ -5380,19 +5380,19 @@
         <v>108</v>
       </c>
       <c r="M33" t="n">
-        <v>16.53</v>
+        <v>16.42</v>
       </c>
       <c r="N33" t="n">
-        <v>14.09</v>
+        <v>14.02</v>
       </c>
       <c r="O33" t="n">
-        <v>30.84</v>
+        <v>30.65</v>
       </c>
       <c r="P33" t="n">
-        <v>7.89</v>
+        <v>7.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.93</v>
+        <v>4.9</v>
       </c>
       <c r="R33" t="n">
         <v>-2.1</v>
@@ -5489,13 +5489,13 @@
         <v>112</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="N34" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="O34" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="P34" t="n">
         <v>1.78</v>
@@ -5504,7 +5504,7 @@
         <v>1.35</v>
       </c>
       <c r="R34" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="S34" t="n">
         <v>105.1</v>
@@ -5598,22 +5598,22 @@
         <v>114</v>
       </c>
       <c r="M35" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="N35" t="n">
-        <v>7.84</v>
+        <v>7.82</v>
       </c>
       <c r="O35" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="P35" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="S35" t="n">
         <v>105.6</v>
@@ -5709,19 +5709,19 @@
         <v>100</v>
       </c>
       <c r="M36" t="n">
-        <v>6.32</v>
+        <v>6.37</v>
       </c>
       <c r="N36" t="n">
-        <v>6.3</v>
+        <v>6.34</v>
       </c>
       <c r="O36" t="n">
-        <v>6.88</v>
+        <v>6.94</v>
       </c>
       <c r="P36" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
         <v>-1</v>
@@ -5818,22 +5818,22 @@
         <v>117</v>
       </c>
       <c r="M37" t="n">
-        <v>6.75</v>
+        <v>6.74</v>
       </c>
       <c r="N37" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="O37" t="n">
         <v>10.7</v>
       </c>
       <c r="P37" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="Q37" t="n">
         <v>2.08</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="S37" t="n">
         <v>107.6</v>
@@ -5927,19 +5927,19 @@
         <v>48</v>
       </c>
       <c r="M38" t="n">
-        <v>11.89</v>
+        <v>11.85</v>
       </c>
       <c r="N38" t="n">
-        <v>17.15</v>
+        <v>17.09</v>
       </c>
       <c r="O38" t="n">
-        <v>10.85</v>
+        <v>10.82</v>
       </c>
       <c r="P38" t="n">
-        <v>5.68</v>
+        <v>5.66</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="R38" t="n">
         <v>-1.9</v>
@@ -6030,22 +6030,22 @@
         <v>120</v>
       </c>
       <c r="M39" t="n">
-        <v>15.67</v>
+        <v>15.83</v>
       </c>
       <c r="N39" t="n">
-        <v>13.85</v>
+        <v>14.03</v>
       </c>
       <c r="O39" t="n">
-        <v>21.31</v>
+        <v>21.58</v>
       </c>
       <c r="P39" t="n">
-        <v>6.97</v>
+        <v>7.03</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
       <c r="R39" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="S39" t="n">
         <v>100.9</v>
@@ -6139,17 +6139,17 @@
         <v>122</v>
       </c>
       <c r="M40" t="n">
-        <v>24.26</v>
+        <v>24.32</v>
       </c>
       <c r="N40"/>
       <c r="O40" t="n">
-        <v>22.29</v>
+        <v>22.37</v>
       </c>
       <c r="P40" t="n">
-        <v>11.37</v>
+        <v>11.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="R40" t="n">
         <v>-3.2</v>
@@ -6232,17 +6232,17 @@
         <v>60</v>
       </c>
       <c r="M41" t="n">
-        <v>36.64</v>
+        <v>36.77</v>
       </c>
       <c r="N41"/>
       <c r="O41" t="n">
-        <v>40</v>
+        <v>40.21</v>
       </c>
       <c r="P41" t="n">
-        <v>17.55</v>
+        <v>17.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>10.63</v>
+        <v>10.65</v>
       </c>
       <c r="R41" t="n">
         <v>-4</v>
@@ -6325,13 +6325,13 @@
         <v>56</v>
       </c>
       <c r="M42" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="O42" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="P42" t="n">
         <v>2.02</v>
@@ -6436,19 +6436,19 @@
         <v>56</v>
       </c>
       <c r="M43" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="N43" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="O43" t="n">
-        <v>7.05</v>
+        <v>7.01</v>
       </c>
       <c r="P43" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R43" t="n">
         <v>-0.6</v>
@@ -6547,19 +6547,19 @@
         <v>129</v>
       </c>
       <c r="M44" t="n">
-        <v>5.96</v>
+        <v>5.93</v>
       </c>
       <c r="N44" t="n">
-        <v>4.95</v>
+        <v>4.94</v>
       </c>
       <c r="O44" t="n">
-        <v>6.86</v>
+        <v>6.83</v>
       </c>
       <c r="P44" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R44" t="n">
         <v>-0.8</v>
@@ -6656,19 +6656,19 @@
         <v>88</v>
       </c>
       <c r="M45" t="n">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="N45" t="n">
         <v>10.19</v>
       </c>
       <c r="O45" t="n">
-        <v>6.37</v>
+        <v>6.36</v>
       </c>
       <c r="P45" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R45" t="n">
         <v>-0.9</v>
@@ -6767,19 +6767,19 @@
         <v>132</v>
       </c>
       <c r="M46" t="n">
-        <v>9.26</v>
+        <v>9.34</v>
       </c>
       <c r="N46" t="n">
-        <v>10.98</v>
+        <v>11.07</v>
       </c>
       <c r="O46" t="n">
-        <v>5.69</v>
+        <v>5.73</v>
       </c>
       <c r="P46" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R46" t="n">
         <v>-1.2</v>
@@ -6878,19 +6878,19 @@
         <v>134</v>
       </c>
       <c r="M47" t="n">
-        <v>15.72</v>
+        <v>15.78</v>
       </c>
       <c r="N47" t="n">
-        <v>20.21</v>
+        <v>20.27</v>
       </c>
       <c r="O47" t="n">
-        <v>11.77</v>
+        <v>11.81</v>
       </c>
       <c r="P47" t="n">
-        <v>7.35</v>
+        <v>7.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="R47" t="n">
         <v>-1.8</v>
@@ -6989,19 +6989,19 @@
         <v>136</v>
       </c>
       <c r="M48" t="n">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="N48" t="n">
-        <v>16.4</v>
+        <v>16.36</v>
       </c>
       <c r="O48" t="n">
-        <v>35.21</v>
+        <v>35.06</v>
       </c>
       <c r="P48" t="n">
-        <v>9.6</v>
+        <v>9.56</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.61</v>
+        <v>5.59</v>
       </c>
       <c r="R48" t="n">
         <v>-2.6</v>
@@ -7098,19 +7098,19 @@
         <v>76</v>
       </c>
       <c r="M49" t="n">
-        <v>50.58</v>
+        <v>51.17</v>
       </c>
       <c r="N49" t="n">
-        <v>52.72</v>
+        <v>53.28</v>
       </c>
       <c r="O49" t="n">
-        <v>74.99</v>
+        <v>75.77</v>
       </c>
       <c r="P49" t="n">
-        <v>22.84</v>
+        <v>23.13</v>
       </c>
       <c r="Q49" t="n">
-        <v>13.3</v>
+        <v>13.46</v>
       </c>
       <c r="R49" t="n">
         <v>-3.5</v>
@@ -7212,7 +7212,7 @@
         <v>1.83</v>
       </c>
       <c r="N50" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O50" t="n">
         <v>1.91</v>
@@ -7320,16 +7320,16 @@
         <v>142</v>
       </c>
       <c r="M51" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="N51" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="O51" t="n">
-        <v>4.64</v>
+        <v>4.68</v>
       </c>
       <c r="P51" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q51" t="n">
         <v>1.28</v>
@@ -7440,7 +7440,7 @@
         <v>5.95</v>
       </c>
       <c r="P52" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="Q52" t="n">
         <v>1.59</v>
@@ -7542,19 +7542,19 @@
         <v>145</v>
       </c>
       <c r="M53" t="n">
-        <v>27.34</v>
+        <v>27.53</v>
       </c>
       <c r="N53" t="n">
-        <v>28.04</v>
+        <v>28.15</v>
       </c>
       <c r="O53" t="n">
-        <v>25.83</v>
+        <v>25.97</v>
       </c>
       <c r="P53" t="n">
-        <v>9.93</v>
+        <v>9.97</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="R53" t="n">
         <v>-3.8</v>
@@ -7653,16 +7653,16 @@
         <v>58</v>
       </c>
       <c r="M54" t="n">
-        <v>33.68</v>
+        <v>33.74</v>
       </c>
       <c r="N54" t="n">
-        <v>28.05</v>
+        <v>28.01</v>
       </c>
       <c r="O54" t="n">
-        <v>53.85</v>
+        <v>53.94</v>
       </c>
       <c r="P54" t="n">
-        <v>11.8</v>
+        <v>11.81</v>
       </c>
       <c r="Q54" t="n">
         <v>5.41</v>
@@ -7764,19 +7764,19 @@
         <v>58</v>
       </c>
       <c r="M55" t="n">
-        <v>46.75</v>
+        <v>46.41</v>
       </c>
       <c r="N55" t="n">
-        <v>45.48</v>
+        <v>45.11</v>
       </c>
       <c r="O55" t="n">
-        <v>42.77</v>
+        <v>42.49</v>
       </c>
       <c r="P55" t="n">
-        <v>16.5</v>
+        <v>16.32</v>
       </c>
       <c r="Q55" t="n">
-        <v>7.63</v>
+        <v>7.57</v>
       </c>
       <c r="R55" t="n">
         <v>-4.4</v>
@@ -7875,19 +7875,19 @@
         <v>58</v>
       </c>
       <c r="M56" t="n">
-        <v>56.02</v>
+        <v>55.6</v>
       </c>
       <c r="N56" t="n">
-        <v>46.75</v>
+        <v>46.36</v>
       </c>
       <c r="O56" t="n">
-        <v>76.47</v>
+        <v>75.91</v>
       </c>
       <c r="P56" t="n">
-        <v>19.16</v>
+        <v>18.96</v>
       </c>
       <c r="Q56" t="n">
-        <v>8.41</v>
+        <v>8.33</v>
       </c>
       <c r="R56" t="n">
         <v>-4.8</v>
@@ -7986,13 +7986,13 @@
         <v>58</v>
       </c>
       <c r="M57" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="N57" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="O57" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="P57" t="n">
         <v>1.66</v>
@@ -8097,19 +8097,19 @@
         <v>114</v>
       </c>
       <c r="M58" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="N58" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="O58" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="P58" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R58" t="n">
         <v>-0.5</v>
@@ -8208,19 +8208,19 @@
         <v>153</v>
       </c>
       <c r="M59" t="n">
-        <v>11.35</v>
+        <v>11.27</v>
       </c>
       <c r="N59" t="n">
-        <v>11.31</v>
+        <v>11.24</v>
       </c>
       <c r="O59" t="n">
-        <v>14.78</v>
+        <v>14.64</v>
       </c>
       <c r="P59" t="n">
-        <v>5.34</v>
+        <v>5.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="R59" t="n">
         <v>-2.2</v>
@@ -8311,16 +8311,16 @@
         <v>155</v>
       </c>
       <c r="M60" t="n">
-        <v>12.22</v>
+        <v>12.23</v>
       </c>
       <c r="N60" t="n">
-        <v>13.06</v>
+        <v>13.07</v>
       </c>
       <c r="O60" t="n">
         <v>23.6</v>
       </c>
       <c r="P60" t="n">
-        <v>5.35</v>
+        <v>5.36</v>
       </c>
       <c r="Q60" t="n">
         <v>3.1</v>
@@ -8422,19 +8422,19 @@
         <v>122</v>
       </c>
       <c r="M61" t="n">
-        <v>12.44</v>
+        <v>12.38</v>
       </c>
       <c r="N61" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="O61" t="n">
-        <v>22.05</v>
+        <v>21.93</v>
       </c>
       <c r="P61" t="n">
-        <v>5.9</v>
+        <v>5.88</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="R61" t="n">
         <v>-2.5</v>
@@ -8525,17 +8525,17 @@
         <v>60</v>
       </c>
       <c r="M62" t="n">
-        <v>18.51</v>
+        <v>18.4</v>
       </c>
       <c r="N62"/>
       <c r="O62" t="n">
-        <v>17.53</v>
+        <v>17.38</v>
       </c>
       <c r="P62" t="n">
-        <v>8.59</v>
+        <v>8.54</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.05</v>
+        <v>5.03</v>
       </c>
       <c r="R62" t="n">
         <v>-3</v>
@@ -8609,76 +8609,76 @@
       </c>
       <c r="I63"/>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K63" t="s">
         <v>158</v>
       </c>
       <c r="L63" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="M63" t="n">
-        <v>20.75</v>
+        <v>20.63</v>
       </c>
       <c r="N63" t="n">
-        <v>17.92</v>
+        <v>24.9</v>
       </c>
       <c r="O63" t="n">
-        <v>43.97</v>
+        <v>26.42</v>
       </c>
       <c r="P63" t="n">
-        <v>8.7</v>
+        <v>9.19</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.82</v>
+        <v>5.2</v>
       </c>
       <c r="R63" t="n">
-        <v>-3.1</v>
+        <v>-3</v>
       </c>
       <c r="S63" t="n">
-        <v>98.6</v>
+        <v>97.9</v>
       </c>
       <c r="T63" t="n">
-        <v>100.7</v>
+        <v>103.1</v>
       </c>
       <c r="U63" t="n">
         <v>98.7</v>
       </c>
       <c r="V63" t="n">
-        <v>104.9</v>
+        <v>103.3</v>
       </c>
       <c r="W63" t="n">
-        <v>99.6</v>
+        <v>100</v>
       </c>
       <c r="X63" t="n">
-        <v>100.6</v>
+        <v>97.9</v>
       </c>
       <c r="Y63" t="n">
-        <v>100.6</v>
+        <v>97.9</v>
       </c>
       <c r="Z63" t="n">
-        <v>100.7</v>
+        <v>97.9</v>
       </c>
       <c r="AA63" t="n">
-        <v>106.1</v>
+        <v>97.9</v>
       </c>
       <c r="AB63" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AE63" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="AF63" t="n">
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="AH63" t="n">
         <v>0</v>
@@ -8720,76 +8720,76 @@
       </c>
       <c r="I64"/>
       <c r="J64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K64" t="s">
+        <v>159</v>
+      </c>
+      <c r="L64" t="s">
         <v>160</v>
       </c>
-      <c r="L64" t="s">
-        <v>134</v>
-      </c>
       <c r="M64" t="n">
-        <v>20.76</v>
+        <v>20.85</v>
       </c>
       <c r="N64" t="n">
-        <v>25.05</v>
+        <v>17.99</v>
       </c>
       <c r="O64" t="n">
-        <v>26.62</v>
+        <v>44.13</v>
       </c>
       <c r="P64" t="n">
-        <v>9.24</v>
+        <v>8.73</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.23</v>
+        <v>4.84</v>
       </c>
       <c r="R64" t="n">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
       <c r="S64" t="n">
-        <v>97.9</v>
+        <v>98.6</v>
       </c>
       <c r="T64" t="n">
-        <v>103.1</v>
+        <v>100.7</v>
       </c>
       <c r="U64" t="n">
         <v>98.7</v>
       </c>
       <c r="V64" t="n">
-        <v>103.3</v>
+        <v>104.9</v>
       </c>
       <c r="W64" t="n">
-        <v>100</v>
+        <v>99.6</v>
       </c>
       <c r="X64" t="n">
-        <v>97.9</v>
+        <v>100.6</v>
       </c>
       <c r="Y64" t="n">
-        <v>97.9</v>
+        <v>100.6</v>
       </c>
       <c r="Z64" t="n">
-        <v>97.9</v>
+        <v>100.7</v>
       </c>
       <c r="AA64" t="n">
-        <v>97.9</v>
+        <v>106.1</v>
       </c>
       <c r="AB64" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AC64" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AD64" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AE64" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="AH64" t="n">
         <v>0</v>
@@ -8840,13 +8840,13 @@
         <v>102</v>
       </c>
       <c r="M65" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="N65" t="n">
         <v>1.86</v>
       </c>
       <c r="O65" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P65" t="n">
         <v>1.22</v>
@@ -8949,16 +8949,16 @@
         <v>62</v>
       </c>
       <c r="M66" t="n">
-        <v>4.79</v>
+        <v>4.82</v>
       </c>
       <c r="N66" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="O66" t="n">
-        <v>8.6</v>
+        <v>8.66</v>
       </c>
       <c r="P66" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q66" t="n">
         <v>1.3</v>
@@ -9060,19 +9060,19 @@
         <v>165</v>
       </c>
       <c r="M67" t="n">
-        <v>11.99</v>
+        <v>11.95</v>
       </c>
       <c r="N67" t="n">
-        <v>11.33</v>
+        <v>11.29</v>
       </c>
       <c r="O67" t="n">
-        <v>14.91</v>
+        <v>14.88</v>
       </c>
       <c r="P67" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R67" t="n">
         <v>-2.9</v>
@@ -9168,25 +9168,25 @@
         <v>166</v>
       </c>
       <c r="L68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M68" t="n">
-        <v>22.15</v>
+        <v>22.22</v>
       </c>
       <c r="N68" t="n">
-        <v>19.54</v>
+        <v>19.61</v>
       </c>
       <c r="O68" t="n">
-        <v>57.88</v>
+        <v>58.15</v>
       </c>
       <c r="P68" t="n">
-        <v>7.79</v>
+        <v>7.81</v>
       </c>
       <c r="Q68" t="n">
         <v>3.75</v>
       </c>
       <c r="R68" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="S68" t="n">
         <v>102.2</v>
@@ -9283,16 +9283,16 @@
         <v>23.46</v>
       </c>
       <c r="N69" t="n">
-        <v>28.86</v>
+        <v>28.88</v>
       </c>
       <c r="O69" t="n">
-        <v>28.41</v>
+        <v>28.44</v>
       </c>
       <c r="P69" t="n">
-        <v>9.19</v>
+        <v>9.18</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
       <c r="R69" t="n">
         <v>-4</v>
@@ -9383,20 +9383,20 @@
         <v>60</v>
       </c>
       <c r="M70" t="n">
-        <v>27.76</v>
+        <v>28.01</v>
       </c>
       <c r="N70"/>
       <c r="O70" t="n">
-        <v>25.19</v>
+        <v>25.54</v>
       </c>
       <c r="P70" t="n">
-        <v>11.07</v>
+        <v>11.17</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="R70" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="S70"/>
       <c r="T70"/>
@@ -9476,19 +9476,19 @@
         <v>56</v>
       </c>
       <c r="M71" t="n">
-        <v>35.4</v>
+        <v>35.33</v>
       </c>
       <c r="N71" t="n">
-        <v>38.39</v>
+        <v>38.36</v>
       </c>
       <c r="O71" t="n">
-        <v>68.49</v>
+        <v>68.42</v>
       </c>
       <c r="P71" t="n">
-        <v>12.58</v>
+        <v>12.54</v>
       </c>
       <c r="Q71" t="n">
-        <v>5.95</v>
+        <v>5.93</v>
       </c>
       <c r="R71" t="n">
         <v>-4.5</v>
@@ -9587,19 +9587,19 @@
         <v>171</v>
       </c>
       <c r="M72" t="n">
-        <v>194.66</v>
+        <v>195.85</v>
       </c>
       <c r="N72" t="n">
-        <v>281.71</v>
+        <v>283.31</v>
       </c>
       <c r="O72" t="n">
-        <v>234.92</v>
+        <v>237.37</v>
       </c>
       <c r="P72" t="n">
-        <v>74.94</v>
+        <v>75.52</v>
       </c>
       <c r="Q72" t="n">
-        <v>34.94</v>
+        <v>35.13</v>
       </c>
       <c r="R72" t="n">
         <v>-7.4</v>
@@ -9699,7 +9699,7 @@
         <v>3.01</v>
       </c>
       <c r="N73" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="O73" t="n">
         <v>2.73</v>
@@ -9805,19 +9805,19 @@
         <v>120</v>
       </c>
       <c r="M74" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="N74" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
       <c r="O74" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="P74" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R74" t="n">
         <v>-0.4</v>
@@ -9914,16 +9914,16 @@
         <v>165</v>
       </c>
       <c r="M75" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="N75" t="n">
-        <v>5.04</v>
+        <v>5.05</v>
       </c>
       <c r="O75" t="n">
-        <v>5.97</v>
+        <v>6</v>
       </c>
       <c r="P75" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="Q75" t="n">
         <v>1.51</v>
@@ -10025,19 +10025,19 @@
         <v>76</v>
       </c>
       <c r="M76" t="n">
-        <v>13.27</v>
+        <v>13.25</v>
       </c>
       <c r="N76" t="n">
-        <v>13.05</v>
+        <v>12.99</v>
       </c>
       <c r="O76" t="n">
-        <v>18.62</v>
+        <v>18.59</v>
       </c>
       <c r="P76" t="n">
-        <v>5.78</v>
+        <v>5.77</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="R76" t="n">
         <v>-2.2</v>
@@ -10134,19 +10134,19 @@
         <v>85</v>
       </c>
       <c r="M77" t="n">
-        <v>19.3</v>
+        <v>19.22</v>
       </c>
       <c r="N77" t="n">
-        <v>20.72</v>
+        <v>20.67</v>
       </c>
       <c r="O77" t="n">
-        <v>34.08</v>
+        <v>33.92</v>
       </c>
       <c r="P77" t="n">
-        <v>9.25</v>
+        <v>9.21</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="R77" t="n">
         <v>-3</v>
@@ -10237,19 +10237,19 @@
         <v>171</v>
       </c>
       <c r="M78" t="n">
-        <v>21.63</v>
+        <v>21.77</v>
       </c>
       <c r="N78" t="n">
-        <v>30.41</v>
+        <v>30.69</v>
       </c>
       <c r="O78" t="n">
-        <v>35.82</v>
+        <v>36.09</v>
       </c>
       <c r="P78" t="n">
-        <v>9.32</v>
+        <v>9.38</v>
       </c>
       <c r="Q78" t="n">
-        <v>5.1</v>
+        <v>5.13</v>
       </c>
       <c r="R78" t="n">
         <v>-2.8</v>
@@ -10346,17 +10346,17 @@
         <v>112</v>
       </c>
       <c r="M79" t="n">
-        <v>28.43</v>
+        <v>28.7</v>
       </c>
       <c r="N79"/>
       <c r="O79" t="n">
-        <v>27.44</v>
+        <v>27.74</v>
       </c>
       <c r="P79" t="n">
-        <v>12.83</v>
+        <v>12.94</v>
       </c>
       <c r="Q79" t="n">
-        <v>7.23</v>
+        <v>7.3</v>
       </c>
       <c r="R79" t="n">
         <v>-3.3</v>
@@ -21166,13 +21166,13 @@
         <v>361</v>
       </c>
       <c r="M179" t="n">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
       <c r="N179" t="n">
-        <v>7.95</v>
+        <v>7.94</v>
       </c>
       <c r="O179" t="n">
-        <v>11.62</v>
+        <v>11.63</v>
       </c>
       <c r="P179" t="n">
         <v>3.36</v>
@@ -21286,7 +21286,7 @@
         <v>9.7</v>
       </c>
       <c r="P180" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="Q180" t="n">
         <v>2.37</v>
@@ -21388,22 +21388,22 @@
         <v>365</v>
       </c>
       <c r="M181" t="n">
-        <v>45.55</v>
+        <v>45.81</v>
       </c>
       <c r="N181" t="n">
-        <v>35.48</v>
+        <v>35.68</v>
       </c>
       <c r="O181" t="n">
-        <v>59.8</v>
+        <v>60.08</v>
       </c>
       <c r="P181" t="n">
-        <v>19.36</v>
+        <v>19.47</v>
       </c>
       <c r="Q181" t="n">
-        <v>10.53</v>
+        <v>10.58</v>
       </c>
       <c r="R181" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="S181" t="n">
         <v>88.8</v>
@@ -21499,13 +21499,13 @@
         <v>365</v>
       </c>
       <c r="M182" t="n">
-        <v>54.6</v>
+        <v>54.59</v>
       </c>
       <c r="N182" t="n">
         <v>41.83</v>
       </c>
       <c r="O182" t="n">
-        <v>68.81</v>
+        <v>68.8</v>
       </c>
       <c r="P182" t="n">
         <v>23.44</v>
@@ -21610,16 +21610,16 @@
         <v>368</v>
       </c>
       <c r="M183" t="n">
-        <v>92.17</v>
+        <v>92.15</v>
       </c>
       <c r="N183" t="n">
-        <v>94.97</v>
+        <v>94.79</v>
       </c>
       <c r="O183" t="n">
-        <v>72.09</v>
+        <v>72.07</v>
       </c>
       <c r="P183" t="n">
-        <v>39.25</v>
+        <v>39.24</v>
       </c>
       <c r="Q183" t="n">
         <v>21.27</v>
@@ -22051,10 +22051,10 @@
         <v>15.68</v>
       </c>
       <c r="N187" t="n">
-        <v>16.35</v>
+        <v>16.34</v>
       </c>
       <c r="O187" t="n">
-        <v>25.66</v>
+        <v>25.68</v>
       </c>
       <c r="P187" t="n">
         <v>6.07</v>
@@ -22063,7 +22063,7 @@
         <v>2.95</v>
       </c>
       <c r="R187" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="S187" t="n">
         <v>88.3</v>
@@ -22162,10 +22162,10 @@
         <v>21.41</v>
       </c>
       <c r="N188" t="n">
-        <v>38.19</v>
+        <v>38.16</v>
       </c>
       <c r="O188" t="n">
-        <v>35.31</v>
+        <v>35.3</v>
       </c>
       <c r="P188" t="n">
         <v>8.24</v>
@@ -22270,19 +22270,19 @@
         <v>368</v>
       </c>
       <c r="M189" t="n">
-        <v>40.1</v>
+        <v>40.29</v>
       </c>
       <c r="N189" t="n">
-        <v>44.35</v>
+        <v>44.55</v>
       </c>
       <c r="O189" t="n">
-        <v>59.05</v>
+        <v>59.32</v>
       </c>
       <c r="P189" t="n">
-        <v>15.13</v>
+        <v>15.2</v>
       </c>
       <c r="Q189" t="n">
-        <v>6.71</v>
+        <v>6.74</v>
       </c>
       <c r="R189" t="n">
         <v>-3.7</v>
@@ -22381,7 +22381,7 @@
         <v>381</v>
       </c>
       <c r="M190" t="n">
-        <v>143.65</v>
+        <v>143.62</v>
       </c>
       <c r="N190" t="n">
         <v>169.79</v>
@@ -22390,10 +22390,10 @@
         <v>42.32</v>
       </c>
       <c r="P190" t="n">
-        <v>56.95</v>
+        <v>56.93</v>
       </c>
       <c r="Q190" t="n">
-        <v>26.32</v>
+        <v>26.31</v>
       </c>
       <c r="R190" t="n">
         <v>-5.4</v>
@@ -22603,7 +22603,7 @@
         <v>117</v>
       </c>
       <c r="M192" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="N192" t="n">
         <v>4.87</v>
@@ -22714,7 +22714,7 @@
         <v>363</v>
       </c>
       <c r="M193" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="N193" t="n">
         <v>4</v>
@@ -22828,7 +22828,7 @@
         <v>7.62</v>
       </c>
       <c r="N194" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="O194" t="n">
         <v>3.9</v>
@@ -22926,19 +22926,19 @@
         <v>361</v>
       </c>
       <c r="M195" t="n">
-        <v>31.86</v>
+        <v>31.98</v>
       </c>
       <c r="N195" t="n">
-        <v>28.68</v>
+        <v>28.81</v>
       </c>
       <c r="O195" t="n">
-        <v>11.81</v>
+        <v>11.86</v>
       </c>
       <c r="P195" t="n">
-        <v>14.21</v>
+        <v>14.27</v>
       </c>
       <c r="Q195" t="n">
-        <v>7.87</v>
+        <v>7.91</v>
       </c>
       <c r="R195" t="n">
         <v>-3.2</v>
@@ -23031,19 +23031,19 @@
         <v>368</v>
       </c>
       <c r="M196" t="n">
-        <v>34.51</v>
+        <v>34.5</v>
       </c>
       <c r="N196" t="n">
         <v>25.39</v>
       </c>
       <c r="O196" t="n">
-        <v>50.02</v>
+        <v>49.99</v>
       </c>
       <c r="P196" t="n">
         <v>14.59</v>
       </c>
       <c r="Q196" t="n">
-        <v>7.6</v>
+        <v>7.59</v>
       </c>
       <c r="R196" t="n">
         <v>-3.3</v>
@@ -23142,19 +23142,19 @@
         <v>391</v>
       </c>
       <c r="M197" t="n">
-        <v>80.37</v>
+        <v>80.35</v>
       </c>
       <c r="N197" t="n">
         <v>97.95</v>
       </c>
       <c r="O197" t="n">
-        <v>81.91</v>
+        <v>81.85</v>
       </c>
       <c r="P197" t="n">
-        <v>34.21</v>
+        <v>34.2</v>
       </c>
       <c r="Q197" t="n">
-        <v>17.55</v>
+        <v>17.54</v>
       </c>
       <c r="R197" t="n">
         <v>-4.1</v>
@@ -23253,19 +23253,19 @@
         <v>368</v>
       </c>
       <c r="M198" t="n">
-        <v>282.98</v>
+        <v>282.93</v>
       </c>
       <c r="N198" t="n">
         <v>196.48</v>
       </c>
       <c r="O198" t="n">
-        <v>286.09</v>
+        <v>285.9</v>
       </c>
       <c r="P198" t="n">
-        <v>126.86</v>
+        <v>126.83</v>
       </c>
       <c r="Q198" t="n">
-        <v>66.99</v>
+        <v>66.97</v>
       </c>
       <c r="R198" t="n">
         <v>-6.2</v>
@@ -23697,13 +23697,13 @@
         <v>401</v>
       </c>
       <c r="M202" t="n">
-        <v>14.74</v>
+        <v>14.73</v>
       </c>
       <c r="N202" t="n">
         <v>14.84</v>
       </c>
       <c r="O202" t="n">
-        <v>14.08</v>
+        <v>14.07</v>
       </c>
       <c r="P202" t="n">
         <v>5.75</v>
@@ -23811,7 +23811,7 @@
         <v>15.24</v>
       </c>
       <c r="N203" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="O203" t="n">
         <v>10.9</v>
@@ -23820,7 +23820,7 @@
         <v>5.87</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="R203" t="n">
         <v>-3</v>
@@ -23919,19 +23919,19 @@
         <v>405</v>
       </c>
       <c r="M204" t="n">
-        <v>25.35</v>
+        <v>25.46</v>
       </c>
       <c r="N204" t="n">
-        <v>23.93</v>
+        <v>24.02</v>
       </c>
       <c r="O204" t="n">
-        <v>31.41</v>
+        <v>31.55</v>
       </c>
       <c r="P204" t="n">
-        <v>9.83</v>
+        <v>9.87</v>
       </c>
       <c r="Q204" t="n">
-        <v>5.23</v>
+        <v>5.25</v>
       </c>
       <c r="R204" t="n">
         <v>-3.5</v>
@@ -24030,7 +24030,7 @@
         <v>368</v>
       </c>
       <c r="M205" t="n">
-        <v>27.39</v>
+        <v>27.38</v>
       </c>
       <c r="N205" t="n">
         <v>22.35</v>
@@ -24141,19 +24141,19 @@
         <v>378</v>
       </c>
       <c r="M206" t="n">
-        <v>255.75</v>
+        <v>255.73</v>
       </c>
       <c r="N206" t="n">
         <v>136.07</v>
       </c>
       <c r="O206" t="n">
-        <v>171.38</v>
+        <v>171.35</v>
       </c>
       <c r="P206" t="n">
-        <v>100.38</v>
+        <v>100.37</v>
       </c>
       <c r="Q206" t="n">
-        <v>51.35</v>
+        <v>51.32</v>
       </c>
       <c r="R206" t="n">
         <v>-7.4</v>
@@ -24366,7 +24366,7 @@
         <v>11.01</v>
       </c>
       <c r="N208" t="n">
-        <v>8.91</v>
+        <v>8.89</v>
       </c>
       <c r="O208" t="n">
         <v>8.1</v>
@@ -24474,16 +24474,16 @@
         <v>368</v>
       </c>
       <c r="M209" t="n">
-        <v>14.33</v>
+        <v>14.32</v>
       </c>
       <c r="N209" t="n">
         <v>10.34</v>
       </c>
       <c r="O209" t="n">
-        <v>20.89</v>
+        <v>20.88</v>
       </c>
       <c r="P209" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="Q209" t="n">
         <v>3</v>
@@ -24585,19 +24585,19 @@
         <v>415</v>
       </c>
       <c r="M210" t="n">
-        <v>14.99</v>
+        <v>15.06</v>
       </c>
       <c r="N210" t="n">
-        <v>10.51</v>
+        <v>10.55</v>
       </c>
       <c r="O210" t="n">
-        <v>10.14</v>
+        <v>10.18</v>
       </c>
       <c r="P210" t="n">
-        <v>5.55</v>
+        <v>5.57</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="R210" t="n">
         <v>-3.4</v>
@@ -24708,7 +24708,7 @@
         <v>5.71</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="R211" t="n">
         <v>-3</v>
@@ -24801,13 +24801,13 @@
         <v>419</v>
       </c>
       <c r="M212" t="n">
-        <v>15.89</v>
+        <v>15.88</v>
       </c>
       <c r="N212" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
       <c r="O212" t="n">
-        <v>22.24</v>
+        <v>22.23</v>
       </c>
       <c r="P212" t="n">
         <v>5.92</v>
@@ -24912,13 +24912,13 @@
         <v>421</v>
       </c>
       <c r="M213" t="n">
-        <v>17.34</v>
+        <v>17.33</v>
       </c>
       <c r="N213" t="n">
         <v>11.75</v>
       </c>
       <c r="O213" t="n">
-        <v>34.39</v>
+        <v>34.37</v>
       </c>
       <c r="P213" t="n">
         <v>6.38</v>
@@ -25023,19 +25023,19 @@
         <v>423</v>
       </c>
       <c r="M214" t="n">
-        <v>32.41</v>
+        <v>32.4</v>
       </c>
       <c r="N214" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="O214" t="n">
-        <v>20.35</v>
+        <v>20.33</v>
       </c>
       <c r="P214" t="n">
         <v>11.56</v>
       </c>
       <c r="Q214" t="n">
-        <v>6.22</v>
+        <v>6.21</v>
       </c>
       <c r="R214" t="n">
         <v>-4.3</v>
@@ -25134,16 +25134,16 @@
         <v>403</v>
       </c>
       <c r="M215" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="N215" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="O215" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="P215" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q215" t="n">
         <v>1.28</v>
@@ -25245,13 +25245,13 @@
         <v>427</v>
       </c>
       <c r="M216" t="n">
-        <v>7.73</v>
+        <v>7.72</v>
       </c>
       <c r="N216" t="n">
         <v>7.32</v>
       </c>
       <c r="O216" t="n">
-        <v>6.7</v>
+        <v>6.69</v>
       </c>
       <c r="P216" t="n">
         <v>3.57</v>
@@ -25356,16 +25356,16 @@
         <v>429</v>
       </c>
       <c r="M217" t="n">
-        <v>7.9</v>
+        <v>7.88</v>
       </c>
       <c r="N217" t="n">
-        <v>5.43</v>
+        <v>5.42</v>
       </c>
       <c r="O217" t="n">
-        <v>8.96</v>
+        <v>8.94</v>
       </c>
       <c r="P217" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="Q217" t="n">
         <v>2.42</v>
@@ -25467,16 +25467,16 @@
         <v>427</v>
       </c>
       <c r="M218" t="n">
-        <v>9.82</v>
+        <v>9.8</v>
       </c>
       <c r="N218" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="O218" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="P218" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="Q218" t="n">
         <v>2.77</v>
@@ -25578,13 +25578,13 @@
         <v>415</v>
       </c>
       <c r="M219" t="n">
-        <v>11.84</v>
+        <v>11.81</v>
       </c>
       <c r="N219" t="n">
-        <v>9.74</v>
+        <v>9.72</v>
       </c>
       <c r="O219" t="n">
-        <v>12.65</v>
+        <v>12.63</v>
       </c>
       <c r="P219" t="n">
         <v>5.28</v>
@@ -25689,16 +25689,16 @@
         <v>433</v>
       </c>
       <c r="M220" t="n">
-        <v>12.43</v>
+        <v>12.41</v>
       </c>
       <c r="N220" t="n">
-        <v>14.05</v>
+        <v>14.03</v>
       </c>
       <c r="O220" t="n">
-        <v>12.37</v>
+        <v>12.35</v>
       </c>
       <c r="P220" t="n">
-        <v>5.46</v>
+        <v>5.45</v>
       </c>
       <c r="Q220" t="n">
         <v>3.26</v>
@@ -25800,19 +25800,19 @@
         <v>429</v>
       </c>
       <c r="M221" t="n">
-        <v>12.91</v>
+        <v>12.88</v>
       </c>
       <c r="N221" t="n">
-        <v>11.47</v>
+        <v>11.45</v>
       </c>
       <c r="O221" t="n">
-        <v>17.37</v>
+        <v>17.35</v>
       </c>
       <c r="P221" t="n">
-        <v>5.64</v>
+        <v>5.63</v>
       </c>
       <c r="Q221" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="R221" t="n">
         <v>-2.4</v>
@@ -25911,19 +25911,19 @@
         <v>373</v>
       </c>
       <c r="M222" t="n">
-        <v>42.55</v>
+        <v>42.47</v>
       </c>
       <c r="N222" t="n">
-        <v>29.3</v>
+        <v>29.23</v>
       </c>
       <c r="O222" t="n">
-        <v>67.37</v>
+        <v>67.27</v>
       </c>
       <c r="P222" t="n">
-        <v>18.41</v>
+        <v>18.39</v>
       </c>
       <c r="Q222" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
       <c r="R222" t="n">
         <v>-4.2</v>
@@ -26244,19 +26244,19 @@
         <v>363</v>
       </c>
       <c r="M225" t="n">
-        <v>13.9</v>
+        <v>13.97</v>
       </c>
       <c r="N225" t="n">
-        <v>14.33</v>
+        <v>14.36</v>
       </c>
       <c r="O225" t="n">
-        <v>16.76</v>
+        <v>16.85</v>
       </c>
       <c r="P225" t="n">
-        <v>5.13</v>
+        <v>5.16</v>
       </c>
       <c r="Q225" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="R225" t="n">
         <v>-3</v>
@@ -26349,19 +26349,19 @@
         <v>442</v>
       </c>
       <c r="M226" t="n">
-        <v>26.06</v>
+        <v>26.05</v>
       </c>
       <c r="N226" t="n">
-        <v>22.51</v>
+        <v>22.5</v>
       </c>
       <c r="O226" t="n">
-        <v>37.75</v>
+        <v>37.74</v>
       </c>
       <c r="P226" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
       <c r="Q226" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="R226" t="n">
         <v>-3.8</v>
@@ -26460,19 +26460,19 @@
         <v>381</v>
       </c>
       <c r="M227" t="n">
-        <v>32.41</v>
+        <v>32.4</v>
       </c>
       <c r="N227" t="n">
         <v>26.96</v>
       </c>
       <c r="O227" t="n">
-        <v>51.35</v>
+        <v>51.34</v>
       </c>
       <c r="P227" t="n">
-        <v>10.89</v>
+        <v>10.88</v>
       </c>
       <c r="Q227" t="n">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
       <c r="R227" t="n">
         <v>-4.2</v>
@@ -26571,19 +26571,19 @@
         <v>445</v>
       </c>
       <c r="M228" t="n">
-        <v>41.1</v>
+        <v>41.09</v>
       </c>
       <c r="N228" t="n">
         <v>36.17</v>
       </c>
       <c r="O228" t="n">
-        <v>63.52</v>
+        <v>63.49</v>
       </c>
       <c r="P228" t="n">
-        <v>15.6</v>
+        <v>15.59</v>
       </c>
       <c r="Q228" t="n">
-        <v>7.44</v>
+        <v>7.43</v>
       </c>
       <c r="R228" t="n">
         <v>-4.7</v>
@@ -26676,19 +26676,19 @@
         <v>447</v>
       </c>
       <c r="M229" t="n">
-        <v>43.26</v>
+        <v>43.25</v>
       </c>
       <c r="N229" t="n">
         <v>29.88</v>
       </c>
       <c r="O229" t="n">
-        <v>116.01</v>
+        <v>115.97</v>
       </c>
       <c r="P229" t="n">
-        <v>14.45</v>
+        <v>14.43</v>
       </c>
       <c r="Q229" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
       <c r="R229" t="n">
         <v>-4.8</v>
@@ -26787,19 +26787,19 @@
         <v>449</v>
       </c>
       <c r="M230" t="n">
-        <v>61.96</v>
+        <v>61.94</v>
       </c>
       <c r="N230" t="n">
         <v>45.48</v>
       </c>
       <c r="O230" t="n">
-        <v>148.29</v>
+        <v>148.24</v>
       </c>
       <c r="P230" t="n">
-        <v>20.83</v>
+        <v>20.82</v>
       </c>
       <c r="Q230" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
       <c r="R230" t="n">
         <v>-5.2</v>
@@ -27123,10 +27123,10 @@
         <v>5.16</v>
       </c>
       <c r="N233" t="n">
-        <v>6.2</v>
+        <v>6.19</v>
       </c>
       <c r="O233" t="n">
-        <v>6.33</v>
+        <v>6.34</v>
       </c>
       <c r="P233" t="n">
         <v>2.62</v>
@@ -27221,19 +27221,19 @@
         <v>456</v>
       </c>
       <c r="M234" t="n">
-        <v>12.62</v>
+        <v>12.67</v>
       </c>
       <c r="N234" t="n">
-        <v>9.71</v>
+        <v>9.73</v>
       </c>
       <c r="O234" t="n">
-        <v>26.94</v>
+        <v>27.08</v>
       </c>
       <c r="P234" t="n">
-        <v>5.85</v>
+        <v>5.87</v>
       </c>
       <c r="Q234" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="R234" t="n">
         <v>-2.1</v>
@@ -27332,7 +27332,7 @@
         <v>447</v>
       </c>
       <c r="M235" t="n">
-        <v>13.41</v>
+        <v>13.4</v>
       </c>
       <c r="N235" t="n">
         <v>11.01</v>
@@ -27443,13 +27443,13 @@
         <v>368</v>
       </c>
       <c r="M236" t="n">
-        <v>14.39</v>
+        <v>14.38</v>
       </c>
       <c r="N236" t="n">
-        <v>17.1</v>
+        <v>17.11</v>
       </c>
       <c r="O236" t="n">
-        <v>12.81</v>
+        <v>12.8</v>
       </c>
       <c r="P236" t="n">
         <v>6.31</v>
@@ -27554,13 +27554,13 @@
         <v>460</v>
       </c>
       <c r="M237" t="n">
-        <v>34.24</v>
+        <v>34.22</v>
       </c>
       <c r="N237" t="n">
         <v>26.56</v>
       </c>
       <c r="O237" t="n">
-        <v>32.84</v>
+        <v>32.83</v>
       </c>
       <c r="P237" t="n">
         <v>15.22</v>
@@ -27665,16 +27665,16 @@
         <v>50</v>
       </c>
       <c r="M238" t="n">
-        <v>53.47</v>
+        <v>53.44</v>
       </c>
       <c r="N238" t="n">
-        <v>42.47</v>
+        <v>42.43</v>
       </c>
       <c r="O238" t="n">
-        <v>65.68</v>
+        <v>65.65</v>
       </c>
       <c r="P238" t="n">
-        <v>23.28</v>
+        <v>23.27</v>
       </c>
       <c r="Q238" t="n">
         <v>12.92</v>
@@ -27776,7 +27776,7 @@
         <v>464</v>
       </c>
       <c r="M239" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="N239" t="n">
         <v>5.14</v>
@@ -27893,13 +27893,13 @@
         <v>4.66</v>
       </c>
       <c r="O240" t="n">
-        <v>8.39</v>
+        <v>8.38</v>
       </c>
       <c r="P240" t="n">
         <v>2.52</v>
       </c>
       <c r="Q240" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R240" t="n">
         <v>-0.4</v>
@@ -28004,10 +28004,10 @@
         <v>5.9</v>
       </c>
       <c r="O241" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="P241" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="Q241" t="n">
         <v>2.12</v>
@@ -28124,7 +28124,7 @@
         <v>2.87</v>
       </c>
       <c r="R242" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="S242" t="n">
         <v>99.4</v>
@@ -28226,7 +28226,7 @@
         <v>8.79</v>
       </c>
       <c r="O243" t="n">
-        <v>23.71</v>
+        <v>23.69</v>
       </c>
       <c r="P243" t="n">
         <v>5.21</v>
@@ -28334,13 +28334,13 @@
         <v>12.01</v>
       </c>
       <c r="N244" t="n">
-        <v>13</v>
+        <v>12.99</v>
       </c>
       <c r="O244" t="n">
-        <v>15.48</v>
+        <v>15.47</v>
       </c>
       <c r="P244" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="Q244" t="n">
         <v>3.44</v>
@@ -28442,19 +28442,19 @@
         <v>460</v>
       </c>
       <c r="M245" t="n">
-        <v>17.46</v>
+        <v>17.53</v>
       </c>
       <c r="N245" t="n">
-        <v>16.15</v>
+        <v>16.21</v>
       </c>
       <c r="O245" t="n">
-        <v>13.28</v>
+        <v>13.34</v>
       </c>
       <c r="P245" t="n">
-        <v>8.04</v>
+        <v>8.08</v>
       </c>
       <c r="Q245" t="n">
-        <v>4.9</v>
+        <v>4.92</v>
       </c>
       <c r="R245" t="n">
         <v>-2.2</v>
@@ -28553,13 +28553,13 @@
         <v>368</v>
       </c>
       <c r="M246" t="n">
-        <v>20.71</v>
+        <v>20.7</v>
       </c>
       <c r="N246" t="n">
-        <v>16.85</v>
+        <v>16.84</v>
       </c>
       <c r="O246" t="n">
-        <v>27.13</v>
+        <v>27.12</v>
       </c>
       <c r="P246" t="n">
         <v>9.41</v>
@@ -28664,16 +28664,16 @@
         <v>361</v>
       </c>
       <c r="M247" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="N247" t="n">
-        <v>4.92</v>
+        <v>4.91</v>
       </c>
       <c r="O247" t="n">
         <v>3.24</v>
       </c>
       <c r="P247" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q247" t="n">
         <v>1.59</v>
@@ -28775,19 +28775,19 @@
         <v>412</v>
       </c>
       <c r="M248" t="n">
-        <v>6.35</v>
+        <v>6.38</v>
       </c>
       <c r="N248" t="n">
-        <v>5.85</v>
+        <v>5.87</v>
       </c>
       <c r="O248" t="n">
-        <v>5.36</v>
+        <v>5.38</v>
       </c>
       <c r="P248" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="Q248" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="R248" t="n">
         <v>-0.8</v>
@@ -28892,7 +28892,7 @@
         <v>6.01</v>
       </c>
       <c r="O249" t="n">
-        <v>13.82</v>
+        <v>13.81</v>
       </c>
       <c r="P249" t="n">
         <v>3.41</v>
@@ -29000,13 +29000,13 @@
         <v>7.3</v>
       </c>
       <c r="N250" t="n">
-        <v>6.31</v>
+        <v>6.3</v>
       </c>
       <c r="O250" t="n">
-        <v>8.97</v>
+        <v>8.96</v>
       </c>
       <c r="P250" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="Q250" t="n">
         <v>2.41</v>
@@ -29108,13 +29108,13 @@
         <v>417</v>
       </c>
       <c r="M251" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="N251" t="n">
-        <v>14.55</v>
+        <v>14.54</v>
       </c>
       <c r="O251" t="n">
-        <v>6.33</v>
+        <v>6.32</v>
       </c>
       <c r="P251" t="n">
         <v>4.86</v>
@@ -29222,7 +29222,7 @@
         <v>10.63</v>
       </c>
       <c r="P252" t="n">
-        <v>6.29</v>
+        <v>6.28</v>
       </c>
       <c r="Q252" t="n">
         <v>3.9</v>
@@ -29324,13 +29324,13 @@
         <v>371</v>
       </c>
       <c r="M253" t="n">
-        <v>14.08</v>
+        <v>14.07</v>
       </c>
       <c r="N253" t="n">
-        <v>11.72</v>
+        <v>11.71</v>
       </c>
       <c r="O253" t="n">
-        <v>21.23</v>
+        <v>21.21</v>
       </c>
       <c r="P253" t="n">
         <v>6.55</v>
@@ -29435,16 +29435,16 @@
         <v>368</v>
       </c>
       <c r="M254" t="n">
-        <v>16.21</v>
+        <v>16.2</v>
       </c>
       <c r="N254" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="O254" t="n">
-        <v>45.23</v>
+        <v>45.19</v>
       </c>
       <c r="P254" t="n">
-        <v>7.36</v>
+        <v>7.35</v>
       </c>
       <c r="Q254" t="n">
         <v>4.48</v>
@@ -29552,7 +29552,7 @@
         <v>3.31</v>
       </c>
       <c r="O255" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="P255" t="n">
         <v>1.96</v>
@@ -29771,7 +29771,7 @@
         <v>5.78</v>
       </c>
       <c r="N257" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="O257" t="n">
         <v>6.68</v>
@@ -29882,7 +29882,7 @@
         <v>6.47</v>
       </c>
       <c r="N258" t="n">
-        <v>10.01</v>
+        <v>10.02</v>
       </c>
       <c r="O258" t="n">
         <v>5.47</v>
@@ -29987,7 +29987,7 @@
         <v>7.01</v>
       </c>
       <c r="N259" t="n">
-        <v>8.25</v>
+        <v>8.26</v>
       </c>
       <c r="O259" t="n">
         <v>5.74</v>
@@ -30095,16 +30095,16 @@
         <v>155</v>
       </c>
       <c r="M260" t="n">
-        <v>37.84</v>
+        <v>37.85</v>
       </c>
       <c r="N260" t="n">
-        <v>28.68</v>
+        <v>28.63</v>
       </c>
       <c r="O260" t="n">
-        <v>51.36</v>
+        <v>51.41</v>
       </c>
       <c r="P260" t="n">
-        <v>16.5</v>
+        <v>16.49</v>
       </c>
       <c r="Q260" t="n">
         <v>9.16</v>
@@ -30209,7 +30209,7 @@
         <v>38.06</v>
       </c>
       <c r="N261" t="n">
-        <v>32.82</v>
+        <v>32.84</v>
       </c>
       <c r="O261" t="n">
         <v>38.69</v>
@@ -30317,19 +30317,19 @@
         <v>391</v>
       </c>
       <c r="M262" t="n">
-        <v>161.68</v>
+        <v>162.03</v>
       </c>
       <c r="N262" t="n">
         <v>98.53</v>
       </c>
       <c r="O262" t="n">
-        <v>328.21</v>
+        <v>329.72</v>
       </c>
       <c r="P262" t="n">
-        <v>72.49</v>
+        <v>72.72</v>
       </c>
       <c r="Q262" t="n">
-        <v>39.59</v>
+        <v>39.7</v>
       </c>
       <c r="R262" t="n">
         <v>-5.6</v>
@@ -30428,7 +30428,7 @@
         <v>384</v>
       </c>
       <c r="M263" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="N263" t="n">
         <v>2.46</v>
@@ -30437,10 +30437,10 @@
         <v>2.45</v>
       </c>
       <c r="P263" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q263" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="R263" t="n">
         <v>1.1</v>
@@ -30542,10 +30542,10 @@
         <v>5</v>
       </c>
       <c r="N264" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="O264" t="n">
-        <v>6.66</v>
+        <v>6.67</v>
       </c>
       <c r="P264" t="n">
         <v>2.3</v>
@@ -30860,7 +30860,7 @@
         <v>12.25</v>
       </c>
       <c r="O267" t="n">
-        <v>12.18</v>
+        <v>12.17</v>
       </c>
       <c r="P267" t="n">
         <v>6.48</v>
@@ -31079,7 +31079,7 @@
         <v>29.7</v>
       </c>
       <c r="N269" t="n">
-        <v>22.5</v>
+        <v>22.54</v>
       </c>
       <c r="O269" t="n">
         <v>25.57</v>
@@ -31187,19 +31187,19 @@
         <v>433</v>
       </c>
       <c r="M270" t="n">
-        <v>149.88</v>
+        <v>150.44</v>
       </c>
       <c r="N270" t="n">
-        <v>94.26</v>
+        <v>95.16</v>
       </c>
       <c r="O270" t="n">
-        <v>192.87</v>
+        <v>193.76</v>
       </c>
       <c r="P270" t="n">
-        <v>61.91</v>
+        <v>62.34</v>
       </c>
       <c r="Q270" t="n">
-        <v>32.39</v>
+        <v>32.56</v>
       </c>
       <c r="R270" t="n">
         <v>-5.9</v>

--- a/files/Straight_Greyhound_upcoming_rated_prices.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices.xlsx
@@ -203,7 +203,7 @@
     <t xml:space="preserve">Corey Mutton</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T12:07:00</t>
+    <t xml:space="preserve">2026-10-11T12:08:00</t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">Claude Dacey</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T13:10:00</t>
+    <t xml:space="preserve">2026-10-11T13:07:00</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>

--- a/files/Straight_Greyhound_upcoming_rated_prices.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices.xlsx
@@ -155,9 +155,6 @@
     <t xml:space="preserve">PROVISIONAL_OR_FINAL</t>
   </si>
   <si>
-    <t xml:space="preserve">BORN CHEEKY</t>
-  </si>
-  <si>
     <t xml:space="preserve">LIL MISS RIPLEY</t>
   </si>
   <si>
@@ -189,6 +186,9 @@
   </si>
   <si>
     <t xml:space="preserve">MOOSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKULI HONEY</t>
   </si>
   <si>
     <t xml:space="preserve">BYE BRUNETTE</t>
@@ -2001,22 +2001,22 @@
         <v>44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="S2" t="n">
         <v>101.2</v>
@@ -2101,29 +2101,29 @@
       </c>
       <c r="I3"/>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K3" t="s">
         <v>47</v>
       </c>
       <c r="L3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9</v>
+        <v>5.72</v>
       </c>
       <c r="N3"/>
       <c r="O3" t="n">
-        <v>3.86</v>
+        <v>4.48</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.3</v>
+        <v>-1.9</v>
       </c>
       <c r="S3"/>
       <c r="T3"/>
@@ -2194,64 +2194,80 @@
       </c>
       <c r="I4"/>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="N4"/>
+        <v>14.62</v>
+      </c>
+      <c r="N4" t="n">
+        <v>11.46</v>
+      </c>
       <c r="O4" t="n">
-        <v>5.94</v>
+        <v>9.84</v>
       </c>
       <c r="P4" t="n">
-        <v>2.92</v>
+        <v>4.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="S4"/>
-      <c r="T4"/>
-      <c r="U4"/>
+        <v>-3.6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>97.5</v>
+      </c>
       <c r="V4" t="n">
-        <v>100</v>
+        <v>102.7</v>
       </c>
       <c r="W4"/>
-      <c r="X4"/>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
+      <c r="X4" t="n">
+        <v>97.4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>97.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>100.2</v>
+      </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
@@ -2287,80 +2303,80 @@
       </c>
       <c r="I5"/>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>18.3</v>
+        <v>17.06</v>
       </c>
       <c r="N5" t="n">
-        <v>14.49</v>
+        <v>14.05</v>
       </c>
       <c r="O5" t="n">
-        <v>13.01</v>
+        <v>15.35</v>
       </c>
       <c r="P5" t="n">
-        <v>6.84</v>
+        <v>5.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.48</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
-        <v>-3.6</v>
+        <v>-3.9</v>
       </c>
       <c r="S5" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="T5" t="n">
         <v>94.7</v>
       </c>
-      <c r="T5" t="n">
-        <v>94.8</v>
-      </c>
       <c r="U5" t="n">
-        <v>97.5</v>
+        <v>94.7</v>
       </c>
       <c r="V5" t="n">
-        <v>102.7</v>
+        <v>100</v>
       </c>
       <c r="W5"/>
       <c r="X5" t="n">
-        <v>97.4</v>
+        <v>94.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>97.4</v>
+        <v>94.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>94.8</v>
+        <v>94.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>100.2</v>
+        <v>94.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
@@ -2396,80 +2412,74 @@
       </c>
       <c r="I6"/>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" t="n">
+        <v>31.48</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="O6" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>90.9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="N6" t="n">
-        <v>17.84</v>
-      </c>
-      <c r="O6" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="P6" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="S6" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>100</v>
-      </c>
-      <c r="W6"/>
-      <c r="X6" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
@@ -2505,46 +2515,46 @@
       </c>
       <c r="I7"/>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" t="s">
         <v>55</v>
       </c>
-      <c r="L7" t="s">
-        <v>56</v>
-      </c>
       <c r="M7" t="n">
-        <v>36.77</v>
+        <v>58.96</v>
       </c>
       <c r="N7" t="n">
-        <v>32.89</v>
+        <v>65.32</v>
       </c>
       <c r="O7" t="n">
-        <v>42.55</v>
+        <v>47.77</v>
       </c>
       <c r="P7" t="n">
-        <v>15.64</v>
+        <v>22.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.4</v>
+        <v>10.44</v>
       </c>
       <c r="R7" t="n">
-        <v>-5.1</v>
+        <v>-6.2</v>
       </c>
       <c r="S7" t="n">
-        <v>90.3</v>
+        <v>89.6</v>
       </c>
       <c r="T7" t="n">
-        <v>90.9</v>
+        <v>88.6</v>
       </c>
       <c r="U7" t="n">
-        <v>90.3</v>
+        <v>88</v>
       </c>
       <c r="V7" t="n">
-        <v>100.6</v>
+        <v>101.4</v>
       </c>
       <c r="W7" t="n">
-        <v>98.2</v>
+        <v>93.3</v>
       </c>
       <c r="X7"/>
       <c r="Y7"/>
@@ -2563,16 +2573,16 @@
         <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
@@ -2608,46 +2618,46 @@
       </c>
       <c r="I8"/>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K8" t="s">
         <v>58</v>
       </c>
       <c r="L8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M8" t="n">
-        <v>73.58</v>
+        <v>71.35</v>
       </c>
       <c r="N8" t="n">
-        <v>79.06</v>
+        <v>83.55</v>
       </c>
       <c r="O8" t="n">
-        <v>63.25</v>
+        <v>52.91</v>
       </c>
       <c r="P8" t="n">
-        <v>30.05</v>
+        <v>25.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.88</v>
+        <v>11.96</v>
       </c>
       <c r="R8" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="S8" t="n">
-        <v>89.6</v>
+        <v>86.4</v>
       </c>
       <c r="T8" t="n">
-        <v>88.6</v>
+        <v>86.4</v>
       </c>
       <c r="U8" t="n">
-        <v>88</v>
+        <v>85.8</v>
       </c>
       <c r="V8" t="n">
-        <v>101.4</v>
+        <v>100.3</v>
       </c>
       <c r="W8" t="n">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
       <c r="X8"/>
       <c r="Y8"/>
@@ -2663,19 +2673,19 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ8" t="s">
         <v>46</v>
@@ -2720,19 +2730,19 @@
         <v>60</v>
       </c>
       <c r="M9" t="n">
-        <v>114.64</v>
+        <v>91.39</v>
       </c>
       <c r="N9" t="n">
-        <v>95.52</v>
+        <v>75.59</v>
       </c>
       <c r="O9" t="n">
-        <v>147.05</v>
+        <v>111.06</v>
       </c>
       <c r="P9" t="n">
-        <v>42.08</v>
+        <v>29.72</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.13</v>
+        <v>13.11</v>
       </c>
       <c r="R9" t="n">
         <v>-6.9</v>
@@ -2786,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ9" t="s">
         <v>46</v>
@@ -2937,22 +2947,22 @@
         <v>65</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>7.34</v>
+        <v>7.32</v>
       </c>
       <c r="N11" t="n">
-        <v>7.16</v>
+        <v>7.13</v>
       </c>
       <c r="O11" t="n">
-        <v>6.67</v>
+        <v>6.65</v>
       </c>
       <c r="P11" t="n">
         <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R11" t="n">
         <v>-2.2</v>
@@ -3004,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ11" t="s">
         <v>46</v>
@@ -3049,10 +3059,10 @@
         <v>67</v>
       </c>
       <c r="M12" t="n">
-        <v>9.61</v>
+        <v>9.59</v>
       </c>
       <c r="N12" t="n">
-        <v>9.54</v>
+        <v>9.52</v>
       </c>
       <c r="O12" t="n">
         <v>5.33</v>
@@ -3115,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ12" t="s">
         <v>46</v>
@@ -3160,17 +3170,17 @@
         <v>69</v>
       </c>
       <c r="M13" t="n">
-        <v>11.81</v>
+        <v>11.82</v>
       </c>
       <c r="N13"/>
       <c r="O13" t="n">
-        <v>8.55</v>
+        <v>8.57</v>
       </c>
       <c r="P13" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
         <v>-2.9</v>
@@ -3253,16 +3263,16 @@
         <v>71</v>
       </c>
       <c r="M14" t="n">
-        <v>24.42</v>
+        <v>24.35</v>
       </c>
       <c r="N14" t="n">
-        <v>25.81</v>
+        <v>25.8</v>
       </c>
       <c r="O14" t="n">
-        <v>12.56</v>
+        <v>12.52</v>
       </c>
       <c r="P14" t="n">
-        <v>8.31</v>
+        <v>8.29</v>
       </c>
       <c r="Q14" t="n">
         <v>4.23</v>
@@ -3319,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="AI14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ14" t="s">
         <v>46</v>
@@ -3364,19 +3374,19 @@
         <v>73</v>
       </c>
       <c r="M15" t="n">
-        <v>26.8</v>
+        <v>26.68</v>
       </c>
       <c r="N15" t="n">
-        <v>31.05</v>
+        <v>30.88</v>
       </c>
       <c r="O15" t="n">
-        <v>21.57</v>
+        <v>21.46</v>
       </c>
       <c r="P15" t="n">
-        <v>9.03</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="R15" t="n">
         <v>-4.1</v>
@@ -3430,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="AI15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ15" t="s">
         <v>46</v>
@@ -3475,19 +3485,19 @@
         <v>75</v>
       </c>
       <c r="M16" t="n">
-        <v>144.14</v>
+        <v>144.22</v>
       </c>
       <c r="N16" t="n">
         <v>142.26</v>
       </c>
       <c r="O16" t="n">
-        <v>214.06</v>
+        <v>214.64</v>
       </c>
       <c r="P16" t="n">
-        <v>55.97</v>
+        <v>56.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.19</v>
+        <v>28.28</v>
       </c>
       <c r="R16" t="n">
         <v>-7.3</v>
@@ -3541,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ16" t="s">
         <v>46</v>
@@ -3586,19 +3596,19 @@
         <v>60</v>
       </c>
       <c r="M17" t="n">
-        <v>197.83</v>
+        <v>197.11</v>
       </c>
       <c r="N17" t="n">
-        <v>257.09</v>
+        <v>255.77</v>
       </c>
       <c r="O17" t="n">
-        <v>208.86</v>
+        <v>207.99</v>
       </c>
       <c r="P17" t="n">
-        <v>70.52</v>
+        <v>70.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.16</v>
+        <v>34.09</v>
       </c>
       <c r="R17" t="n">
         <v>-7.1</v>
@@ -3652,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="AI17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ17" t="s">
         <v>46</v>
@@ -3700,7 +3710,7 @@
         <v>1.38</v>
       </c>
       <c r="N18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="O18" t="n">
         <v>1.32</v>
@@ -3712,7 +3722,7 @@
         <v>1.01</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="S18" t="n">
         <v>99.2</v>
@@ -3761,7 +3771,7 @@
         <v>0</v>
       </c>
       <c r="AI18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ18" t="s">
         <v>46</v>
@@ -3806,13 +3816,13 @@
         <v>83</v>
       </c>
       <c r="M19" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="N19" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="O19" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="P19" t="n">
         <v>1.24</v>
@@ -3821,7 +3831,7 @@
         <v>1.04</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="S19" t="n">
         <v>104.9</v>
@@ -3872,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="AI19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ19" t="s">
         <v>46</v>
@@ -3917,19 +3927,19 @@
         <v>75</v>
       </c>
       <c r="M20" t="n">
-        <v>38.31</v>
+        <v>38.13</v>
       </c>
       <c r="N20" t="n">
-        <v>29.9</v>
+        <v>29.83</v>
       </c>
       <c r="O20" t="n">
-        <v>43.71</v>
+        <v>43.53</v>
       </c>
       <c r="P20" t="n">
-        <v>9.49</v>
+        <v>9.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R20" t="n">
         <v>-4.9</v>
@@ -3983,7 +3993,7 @@
         <v>1</v>
       </c>
       <c r="AI20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ20" t="s">
         <v>46</v>
@@ -4028,19 +4038,19 @@
         <v>73</v>
       </c>
       <c r="M21" t="n">
-        <v>114.3</v>
+        <v>114.46</v>
       </c>
       <c r="N21" t="n">
         <v>60.65</v>
       </c>
       <c r="O21" t="n">
-        <v>102.28</v>
+        <v>102.43</v>
       </c>
       <c r="P21" t="n">
-        <v>25.19</v>
+        <v>25.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.7</v>
+        <v>5.72</v>
       </c>
       <c r="R21" t="n">
         <v>-6.8</v>
@@ -4092,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AI21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ21" t="s">
         <v>46</v>
@@ -4137,19 +4147,19 @@
         <v>87</v>
       </c>
       <c r="M22" t="n">
-        <v>116.35</v>
+        <v>116</v>
       </c>
       <c r="N22" t="n">
-        <v>109.3</v>
+        <v>109.06</v>
       </c>
       <c r="O22" t="n">
-        <v>145.03</v>
+        <v>144.3</v>
       </c>
       <c r="P22" t="n">
-        <v>30.15</v>
+        <v>30.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.83</v>
+        <v>6.81</v>
       </c>
       <c r="R22" t="n">
         <v>-6.3</v>
@@ -4203,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="AI22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ22" t="s">
         <v>46</v>
@@ -4248,19 +4258,19 @@
         <v>71</v>
       </c>
       <c r="M23" t="n">
-        <v>120.79</v>
+        <v>121.1</v>
       </c>
       <c r="N23" t="n">
-        <v>77.34</v>
+        <v>77.46</v>
       </c>
       <c r="O23" t="n">
-        <v>167.19</v>
+        <v>167.47</v>
       </c>
       <c r="P23" t="n">
-        <v>29.11</v>
+        <v>29.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.46</v>
+        <v>6.49</v>
       </c>
       <c r="R23" t="n">
         <v>-6.5</v>
@@ -4314,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="AI23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ23" t="s">
         <v>46</v>
@@ -4359,16 +4369,16 @@
         <v>90</v>
       </c>
       <c r="M24" t="n">
-        <v>139.08</v>
+        <v>139</v>
       </c>
       <c r="N24" t="n">
-        <v>109.3</v>
+        <v>109.06</v>
       </c>
       <c r="O24" t="n">
-        <v>90.89</v>
+        <v>90.66</v>
       </c>
       <c r="P24" t="n">
-        <v>33.94</v>
+        <v>33.98</v>
       </c>
       <c r="Q24" t="n">
         <v>7.43</v>
@@ -4425,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="AI24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ24" t="s">
         <v>46</v>
@@ -4536,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ25" t="s">
         <v>46</v>
@@ -4581,16 +4591,16 @@
         <v>96</v>
       </c>
       <c r="M26" t="n">
-        <v>17.24</v>
+        <v>17.19</v>
       </c>
       <c r="N26" t="n">
-        <v>9.92</v>
+        <v>9.89</v>
       </c>
       <c r="O26" t="n">
-        <v>44.6</v>
+        <v>44.44</v>
       </c>
       <c r="P26" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
         <v>1.46</v>
@@ -4690,19 +4700,19 @@
         <v>90</v>
       </c>
       <c r="M27" t="n">
-        <v>31.79</v>
+        <v>31.93</v>
       </c>
       <c r="N27" t="n">
-        <v>23.13</v>
+        <v>23.24</v>
       </c>
       <c r="O27" t="n">
-        <v>36.08</v>
+        <v>36.22</v>
       </c>
       <c r="P27" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
         <v>-5.1</v>
@@ -4756,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="AI27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ27" t="s">
         <v>46</v>
@@ -4801,16 +4811,16 @@
         <v>99</v>
       </c>
       <c r="M28" t="n">
-        <v>49.73</v>
+        <v>49.66</v>
       </c>
       <c r="N28" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="O28" t="n">
-        <v>113.82</v>
+        <v>113.62</v>
       </c>
       <c r="P28" t="n">
-        <v>5.82</v>
+        <v>5.81</v>
       </c>
       <c r="Q28" t="n">
         <v>2.67</v>
@@ -4867,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="AI28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ28" t="s">
         <v>46</v>
@@ -4912,19 +4922,19 @@
         <v>73</v>
       </c>
       <c r="M29" t="n">
-        <v>73.08</v>
+        <v>73.36</v>
       </c>
       <c r="N29" t="n">
-        <v>43.05</v>
+        <v>43.16</v>
       </c>
       <c r="O29" t="n">
-        <v>265.19</v>
+        <v>266.32</v>
       </c>
       <c r="P29" t="n">
-        <v>9.66</v>
+        <v>9.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="R29" t="n">
         <v>-6.9</v>
@@ -4976,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="AI29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ29" t="s">
         <v>46</v>
@@ -5021,19 +5031,19 @@
         <v>75</v>
       </c>
       <c r="M30" t="n">
-        <v>117.14</v>
+        <v>117</v>
       </c>
       <c r="N30" t="n">
-        <v>87.65</v>
+        <v>87.49</v>
       </c>
       <c r="O30" t="n">
-        <v>200.21</v>
+        <v>199.68</v>
       </c>
       <c r="P30" t="n">
-        <v>14.12</v>
+        <v>14.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.04</v>
+        <v>6.02</v>
       </c>
       <c r="R30" t="n">
         <v>-6.9</v>
@@ -5087,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="AI30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ30" t="s">
         <v>46</v>
@@ -5132,10 +5142,10 @@
         <v>105</v>
       </c>
       <c r="M31" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="N31" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O31" t="n">
         <v>2.61</v>
@@ -5196,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="AI31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ31" t="s">
         <v>46</v>
@@ -5241,13 +5251,13 @@
         <v>96</v>
       </c>
       <c r="M32" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="N32" t="n">
         <v>4.8</v>
       </c>
       <c r="O32" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="P32" t="n">
         <v>1.96</v>
@@ -5299,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="AI32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ32" t="s">
         <v>46</v>
@@ -5344,19 +5354,19 @@
         <v>108</v>
       </c>
       <c r="M33" t="n">
-        <v>6.21</v>
+        <v>6.23</v>
       </c>
       <c r="N33" t="n">
-        <v>5.73</v>
+        <v>5.74</v>
       </c>
       <c r="O33" t="n">
-        <v>8.23</v>
+        <v>8.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R33" t="n">
         <v>-1.4</v>
@@ -5408,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="AI33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ33" t="s">
         <v>46</v>
@@ -5453,19 +5463,19 @@
         <v>60</v>
       </c>
       <c r="M34" t="n">
-        <v>16.66</v>
+        <v>16.73</v>
       </c>
       <c r="N34" t="n">
-        <v>15.13</v>
+        <v>15.22</v>
       </c>
       <c r="O34" t="n">
-        <v>21.13</v>
+        <v>21.19</v>
       </c>
       <c r="P34" t="n">
-        <v>6.69</v>
+        <v>6.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="R34" t="n">
         <v>-2.7</v>
@@ -5519,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="AI34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ34" t="s">
         <v>46</v>
@@ -5564,19 +5574,19 @@
         <v>111</v>
       </c>
       <c r="M35" t="n">
-        <v>23.7</v>
+        <v>23.64</v>
       </c>
       <c r="N35" t="n">
-        <v>22.24</v>
+        <v>22.2</v>
       </c>
       <c r="O35" t="n">
-        <v>20.34</v>
+        <v>20.29</v>
       </c>
       <c r="P35" t="n">
-        <v>9.11</v>
+        <v>9.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="R35" t="n">
         <v>-3.2</v>
@@ -5628,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="AI35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ35" t="s">
         <v>46</v>
@@ -5673,19 +5683,19 @@
         <v>83</v>
       </c>
       <c r="M36" t="n">
-        <v>38.76</v>
+        <v>38.66</v>
       </c>
       <c r="N36" t="n">
-        <v>29.3</v>
+        <v>29.28</v>
       </c>
       <c r="O36" t="n">
-        <v>78.24</v>
+        <v>78.03</v>
       </c>
       <c r="P36" t="n">
-        <v>14.65</v>
+        <v>14.61</v>
       </c>
       <c r="Q36" t="n">
-        <v>7.17</v>
+        <v>7.15</v>
       </c>
       <c r="R36" t="n">
         <v>-4</v>
@@ -5739,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="AI36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ36" t="s">
         <v>46</v>
@@ -5784,19 +5794,19 @@
         <v>114</v>
       </c>
       <c r="M37" t="n">
-        <v>77.14</v>
+        <v>77.12</v>
       </c>
       <c r="N37" t="n">
         <v>49.68</v>
       </c>
       <c r="O37" t="n">
-        <v>118.11</v>
+        <v>118</v>
       </c>
       <c r="P37" t="n">
-        <v>31.27</v>
+        <v>31.22</v>
       </c>
       <c r="Q37" t="n">
-        <v>15.49</v>
+        <v>15.46</v>
       </c>
       <c r="R37" t="n">
         <v>-5.2</v>
@@ -5848,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="AI37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ37" t="s">
         <v>46</v>
@@ -5893,19 +5903,19 @@
         <v>108</v>
       </c>
       <c r="M38" t="n">
-        <v>146.61</v>
+        <v>146.07</v>
       </c>
       <c r="N38" t="n">
-        <v>122.41</v>
+        <v>122.11</v>
       </c>
       <c r="O38" t="n">
-        <v>266.6</v>
+        <v>265.42</v>
       </c>
       <c r="P38" t="n">
-        <v>56.93</v>
+        <v>56.54</v>
       </c>
       <c r="Q38" t="n">
-        <v>27.16</v>
+        <v>27</v>
       </c>
       <c r="R38" t="n">
         <v>-5.7</v>
@@ -5957,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="AI38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ38" t="s">
         <v>46</v>
@@ -6008,7 +6018,7 @@
         <v>1.53</v>
       </c>
       <c r="O39" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P39" t="n">
         <v>1.14</v>
@@ -6066,7 +6076,7 @@
         <v>0</v>
       </c>
       <c r="AI39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ39" t="s">
         <v>46</v>
@@ -6111,16 +6121,16 @@
         <v>122</v>
       </c>
       <c r="M40" t="n">
-        <v>6.66</v>
+        <v>6.64</v>
       </c>
       <c r="N40" t="n">
-        <v>6.28</v>
+        <v>6.27</v>
       </c>
       <c r="O40" t="n">
-        <v>11.35</v>
+        <v>11.33</v>
       </c>
       <c r="P40" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="Q40" t="n">
         <v>1.44</v>
@@ -6175,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="AI40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ40" t="s">
         <v>46</v>
@@ -6220,19 +6230,19 @@
         <v>124</v>
       </c>
       <c r="M41" t="n">
-        <v>16.28</v>
+        <v>16.34</v>
       </c>
       <c r="N41" t="n">
-        <v>19.27</v>
+        <v>19.32</v>
       </c>
       <c r="O41" t="n">
-        <v>10.84</v>
+        <v>10.88</v>
       </c>
       <c r="P41" t="n">
-        <v>5.02</v>
+        <v>5.04</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="R41" t="n">
         <v>-3.1</v>
@@ -6286,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="AI41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ41" t="s">
         <v>46</v>
@@ -6331,19 +6341,19 @@
         <v>90</v>
       </c>
       <c r="M42" t="n">
-        <v>20.07</v>
+        <v>20.03</v>
       </c>
       <c r="N42" t="n">
-        <v>21.05</v>
+        <v>21.01</v>
       </c>
       <c r="O42" t="n">
-        <v>24.55</v>
+        <v>24.5</v>
       </c>
       <c r="P42" t="n">
-        <v>6.34</v>
+        <v>6.32</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="R42" t="n">
         <v>-3.5</v>
@@ -6397,7 +6407,7 @@
         <v>1</v>
       </c>
       <c r="AI42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ42" t="s">
         <v>46</v>
@@ -6442,19 +6452,19 @@
         <v>75</v>
       </c>
       <c r="M43" t="n">
-        <v>20.3</v>
+        <v>20.39</v>
       </c>
       <c r="N43" t="n">
-        <v>20.46</v>
+        <v>20.6</v>
       </c>
       <c r="O43" t="n">
-        <v>23.28</v>
+        <v>23.37</v>
       </c>
       <c r="P43" t="n">
-        <v>6.47</v>
+        <v>6.49</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="R43" t="n">
         <v>-3.5</v>
@@ -6508,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="AI43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ43" t="s">
         <v>46</v>
@@ -6553,19 +6563,19 @@
         <v>44</v>
       </c>
       <c r="M44" t="n">
-        <v>25.85</v>
+        <v>25.79</v>
       </c>
       <c r="N44" t="n">
-        <v>36.59</v>
+        <v>36.54</v>
       </c>
       <c r="O44" t="n">
-        <v>42.44</v>
+        <v>42.32</v>
       </c>
       <c r="P44" t="n">
-        <v>8.09</v>
+        <v>8.07</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="R44" t="n">
         <v>-3.6</v>
@@ -6619,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="AI44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ44" t="s">
         <v>46</v>
@@ -6664,19 +6674,19 @@
         <v>83</v>
       </c>
       <c r="M45" t="n">
-        <v>85.65</v>
+        <v>85.83</v>
       </c>
       <c r="N45" t="n">
-        <v>86.14</v>
+        <v>86.29</v>
       </c>
       <c r="O45" t="n">
-        <v>49.06</v>
+        <v>49.22</v>
       </c>
       <c r="P45" t="n">
-        <v>29.29</v>
+        <v>29.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>14.29</v>
+        <v>14.33</v>
       </c>
       <c r="R45" t="n">
         <v>-5.7</v>
@@ -6779,7 +6789,7 @@
         <v>2.52</v>
       </c>
       <c r="O46" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="P46" t="n">
         <v>1.47</v>
@@ -6837,7 +6847,7 @@
         <v>0</v>
       </c>
       <c r="AI46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ46" t="s">
         <v>46</v>
@@ -6948,7 +6958,7 @@
         <v>1</v>
       </c>
       <c r="AI47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ47" t="s">
         <v>46</v>
@@ -6993,13 +7003,13 @@
         <v>124</v>
       </c>
       <c r="M48" t="n">
-        <v>8.19</v>
+        <v>8.18</v>
       </c>
       <c r="N48" t="n">
-        <v>8.24</v>
+        <v>8.22</v>
       </c>
       <c r="O48" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="P48" t="n">
         <v>3.62</v>
@@ -7059,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="AI48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ48" t="s">
         <v>46</v>
@@ -7104,16 +7114,16 @@
         <v>136</v>
       </c>
       <c r="M49" t="n">
-        <v>8.99</v>
+        <v>9.03</v>
       </c>
       <c r="N49" t="n">
-        <v>8.33</v>
+        <v>8.36</v>
       </c>
       <c r="O49" t="n">
-        <v>11.64</v>
+        <v>11.69</v>
       </c>
       <c r="P49" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="Q49" t="n">
         <v>2.35</v>
@@ -7168,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="AI49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ49" t="s">
         <v>46</v>
@@ -7213,19 +7223,19 @@
         <v>138</v>
       </c>
       <c r="M50" t="n">
-        <v>12.45</v>
+        <v>12.52</v>
       </c>
       <c r="N50" t="n">
-        <v>10.8</v>
+        <v>10.86</v>
       </c>
       <c r="O50" t="n">
-        <v>9.52</v>
+        <v>9.56</v>
       </c>
       <c r="P50" t="n">
-        <v>5.36</v>
+        <v>5.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="R50" t="n">
         <v>-2.3</v>
@@ -7277,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="AI50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ50" t="s">
         <v>46</v>
@@ -7322,22 +7332,22 @@
         <v>73</v>
       </c>
       <c r="M51" t="n">
-        <v>21.97</v>
+        <v>22</v>
       </c>
       <c r="N51" t="n">
-        <v>23</v>
+        <v>23.03</v>
       </c>
       <c r="O51" t="n">
-        <v>33.44</v>
+        <v>33.47</v>
       </c>
       <c r="P51" t="n">
         <v>9.09</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="R51" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="S51" t="n">
         <v>106.1</v>
@@ -7388,7 +7398,7 @@
         <v>0</v>
       </c>
       <c r="AI51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ51" t="s">
         <v>46</v>
@@ -7433,19 +7443,19 @@
         <v>124</v>
       </c>
       <c r="M52" t="n">
-        <v>41.44</v>
+        <v>41.62</v>
       </c>
       <c r="N52" t="n">
-        <v>48.38</v>
+        <v>48.48</v>
       </c>
       <c r="O52" t="n">
-        <v>40.04</v>
+        <v>40.23</v>
       </c>
       <c r="P52" t="n">
-        <v>17.66</v>
+        <v>17.74</v>
       </c>
       <c r="Q52" t="n">
-        <v>9.79</v>
+        <v>9.82</v>
       </c>
       <c r="R52" t="n">
         <v>-3.7</v>
@@ -7499,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="AI52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ52" t="s">
         <v>46</v>
@@ -7547,7 +7557,7 @@
         <v>1.2</v>
       </c>
       <c r="N53" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O53" t="n">
         <v>1.17</v>
@@ -7559,7 +7569,7 @@
         <v>1.02</v>
       </c>
       <c r="R53" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="S53" t="n">
         <v>107.8</v>
@@ -7608,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="AI53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ53" t="s">
         <v>46</v>
@@ -7653,13 +7663,13 @@
         <v>94</v>
       </c>
       <c r="M54" t="n">
-        <v>19</v>
+        <v>19.11</v>
       </c>
       <c r="N54" t="n">
-        <v>15.04</v>
+        <v>15.09</v>
       </c>
       <c r="O54" t="n">
-        <v>23.18</v>
+        <v>23.31</v>
       </c>
       <c r="P54" t="n">
         <v>3.04</v>
@@ -7668,7 +7678,7 @@
         <v>1.73</v>
       </c>
       <c r="R54" t="n">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
       <c r="S54" t="n">
         <v>99.8</v>
@@ -7717,7 +7727,7 @@
         <v>0</v>
       </c>
       <c r="AI54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ54" t="s">
         <v>46</v>
@@ -7762,16 +7772,16 @@
         <v>146</v>
       </c>
       <c r="M55" t="n">
-        <v>26.1</v>
+        <v>26.25</v>
       </c>
       <c r="N55" t="n">
-        <v>24.65</v>
+        <v>24.76</v>
       </c>
       <c r="O55" t="n">
-        <v>35.46</v>
+        <v>35.67</v>
       </c>
       <c r="P55" t="n">
-        <v>4.08</v>
+        <v>4.09</v>
       </c>
       <c r="Q55" t="n">
         <v>2.13</v>
@@ -7871,19 +7881,19 @@
         <v>44</v>
       </c>
       <c r="M56" t="n">
-        <v>34.16</v>
+        <v>34.36</v>
       </c>
       <c r="N56" t="n">
-        <v>25.69</v>
+        <v>25.82</v>
       </c>
       <c r="O56" t="n">
-        <v>38.26</v>
+        <v>38.5</v>
       </c>
       <c r="P56" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="R56" t="n">
         <v>-5</v>
@@ -7935,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="AI56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ56" t="s">
         <v>46</v>
@@ -7980,19 +7990,19 @@
         <v>149</v>
       </c>
       <c r="M57" t="n">
-        <v>47.01</v>
+        <v>46.91</v>
       </c>
       <c r="N57" t="n">
-        <v>44.63</v>
+        <v>44.55</v>
       </c>
       <c r="O57" t="n">
-        <v>33.69</v>
+        <v>33.64</v>
       </c>
       <c r="P57" t="n">
-        <v>6.95</v>
+        <v>6.92</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="R57" t="n">
         <v>-5.2</v>
@@ -8044,7 +8054,7 @@
         <v>1</v>
       </c>
       <c r="AI57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ57" t="s">
         <v>46</v>
@@ -8089,19 +8099,19 @@
         <v>151</v>
       </c>
       <c r="M58" t="n">
-        <v>59.36</v>
+        <v>59.32</v>
       </c>
       <c r="N58" t="n">
-        <v>51.42</v>
+        <v>51.47</v>
       </c>
       <c r="O58" t="n">
-        <v>65.47</v>
+        <v>65.49</v>
       </c>
       <c r="P58" t="n">
-        <v>9.96</v>
+        <v>9.92</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
       <c r="R58" t="n">
         <v>-5.8</v>
@@ -8198,19 +8208,19 @@
         <v>73</v>
       </c>
       <c r="M59" t="n">
-        <v>156.94</v>
+        <v>157.22</v>
       </c>
       <c r="N59" t="n">
-        <v>106.05</v>
+        <v>106.28</v>
       </c>
       <c r="O59" t="n">
-        <v>411.88</v>
+        <v>412.72</v>
       </c>
       <c r="P59" t="n">
-        <v>27.16</v>
+        <v>27.11</v>
       </c>
       <c r="Q59" t="n">
-        <v>12.14</v>
+        <v>12.13</v>
       </c>
       <c r="R59" t="n">
         <v>-7.6</v>
@@ -8262,7 +8272,7 @@
         <v>0</v>
       </c>
       <c r="AI59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ59" t="s">
         <v>46</v>
@@ -8371,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="AI60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ60" t="s">
         <v>46</v>
@@ -8416,16 +8426,16 @@
         <v>105</v>
       </c>
       <c r="M61" t="n">
-        <v>20.25</v>
+        <v>20.27</v>
       </c>
       <c r="N61" t="n">
-        <v>18.31</v>
+        <v>18.33</v>
       </c>
       <c r="O61" t="n">
-        <v>13.08</v>
+        <v>13.09</v>
       </c>
       <c r="P61" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q61" t="n">
         <v>1.04</v>
@@ -8525,16 +8535,16 @@
         <v>158</v>
       </c>
       <c r="M62" t="n">
-        <v>73.28</v>
+        <v>72.64</v>
       </c>
       <c r="N62" t="n">
-        <v>73.48</v>
+        <v>72.73</v>
       </c>
       <c r="O62" t="n">
-        <v>25.57</v>
+        <v>25.39</v>
       </c>
       <c r="P62" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="Q62" t="n">
         <v>1.21</v>
@@ -8591,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="AI62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ62" t="s">
         <v>46</v>
@@ -8636,19 +8646,19 @@
         <v>114</v>
       </c>
       <c r="M63" t="n">
-        <v>417.69</v>
+        <v>415.81</v>
       </c>
       <c r="N63" t="n">
-        <v>283.3</v>
+        <v>281.7</v>
       </c>
       <c r="O63" t="n">
-        <v>214.21</v>
+        <v>213.13</v>
       </c>
       <c r="P63" t="n">
-        <v>32.36</v>
+        <v>32.24</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.68</v>
+        <v>7.69</v>
       </c>
       <c r="R63" t="n">
         <v>-9.2</v>
@@ -8700,7 +8710,7 @@
         <v>1</v>
       </c>
       <c r="AI63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ63" t="s">
         <v>46</v>
@@ -8745,19 +8755,19 @@
         <v>90</v>
       </c>
       <c r="M64" t="n">
-        <v>666.24</v>
+        <v>664.21</v>
       </c>
       <c r="N64" t="n">
         <v>591.75</v>
       </c>
       <c r="O64" t="n">
-        <v>273.54</v>
+        <v>271.9</v>
       </c>
       <c r="P64" t="n">
-        <v>49.11</v>
+        <v>48.86</v>
       </c>
       <c r="Q64" t="n">
-        <v>11.89</v>
+        <v>11.88</v>
       </c>
       <c r="R64" t="n">
         <v>-9.2</v>
@@ -8811,7 +8821,7 @@
         <v>1</v>
       </c>
       <c r="AI64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ64" t="s">
         <v>46</v>
@@ -8969,7 +8979,7 @@
       </c>
       <c r="N66"/>
       <c r="O66" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="P66" t="n">
         <v>2.06</v>
@@ -9058,16 +9068,16 @@
         <v>75</v>
       </c>
       <c r="M67" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
       <c r="N67" t="n">
-        <v>12.45</v>
+        <v>12.44</v>
       </c>
       <c r="O67" t="n">
-        <v>10.35</v>
+        <v>10.32</v>
       </c>
       <c r="P67" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="Q67" t="n">
         <v>1.95</v>
@@ -9124,7 +9134,7 @@
         <v>1</v>
       </c>
       <c r="AI67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ67" t="s">
         <v>46</v>
@@ -9169,19 +9179,19 @@
         <v>83</v>
       </c>
       <c r="M68" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="N68" t="n">
+        <v>9.04</v>
+      </c>
+      <c r="O68" t="n">
         <v>10.43</v>
       </c>
-      <c r="N68" t="n">
-        <v>8.99</v>
-      </c>
-      <c r="O68" t="n">
-        <v>10.37</v>
-      </c>
       <c r="P68" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="R68" t="n">
         <v>-2.7</v>
@@ -9233,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="AI68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ68" t="s">
         <v>46</v>
@@ -9278,16 +9288,16 @@
         <v>158</v>
       </c>
       <c r="M69" t="n">
-        <v>26.21</v>
+        <v>26.24</v>
       </c>
       <c r="N69" t="n">
-        <v>29.46</v>
+        <v>29.49</v>
       </c>
       <c r="O69" t="n">
-        <v>11.95</v>
+        <v>11.97</v>
       </c>
       <c r="P69" t="n">
-        <v>9.63</v>
+        <v>9.64</v>
       </c>
       <c r="Q69" t="n">
         <v>4.66</v>
@@ -9384,22 +9394,22 @@
         <v>167</v>
       </c>
       <c r="L70" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M70" t="n">
-        <v>45.54</v>
+        <v>45.71</v>
       </c>
       <c r="N70" t="n">
-        <v>57.51</v>
+        <v>57.77</v>
       </c>
       <c r="O70" t="n">
-        <v>35.24</v>
+        <v>35.41</v>
       </c>
       <c r="P70" t="n">
-        <v>18.19</v>
+        <v>18.26</v>
       </c>
       <c r="Q70" t="n">
-        <v>9.03</v>
+        <v>9.06</v>
       </c>
       <c r="R70" t="n">
         <v>-5.1</v>
@@ -9445,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="AI70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ70" t="s">
         <v>46</v>
@@ -9556,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="AI71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ71" t="s">
         <v>46</v>
@@ -10463,7 +10473,7 @@
         <v>1</v>
       </c>
       <c r="AI80" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ80" t="s">
         <v>46</v>
@@ -10574,7 +10584,7 @@
         <v>0</v>
       </c>
       <c r="AI81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ81" t="s">
         <v>46</v>
@@ -10685,7 +10695,7 @@
         <v>0</v>
       </c>
       <c r="AI82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ82" t="s">
         <v>46</v>
@@ -10796,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="AI83" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ83" t="s">
         <v>46</v>
@@ -10907,7 +10917,7 @@
         <v>0</v>
       </c>
       <c r="AI84" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ84" t="s">
         <v>46</v>
@@ -11129,7 +11139,7 @@
         <v>0</v>
       </c>
       <c r="AI86" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ86" t="s">
         <v>46</v>
@@ -11240,7 +11250,7 @@
         <v>0</v>
       </c>
       <c r="AI87" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ87" t="s">
         <v>46</v>
@@ -11351,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="AI88" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ88" t="s">
         <v>46</v>
@@ -11462,7 +11472,7 @@
         <v>0</v>
       </c>
       <c r="AI89" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ89" t="s">
         <v>46</v>
@@ -11573,7 +11583,7 @@
         <v>0</v>
       </c>
       <c r="AI90" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ90" t="s">
         <v>46</v>
@@ -11963,7 +11973,7 @@
         <v>0</v>
       </c>
       <c r="AI94" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ94" t="s">
         <v>46</v>
@@ -12171,7 +12181,7 @@
         <v>0</v>
       </c>
       <c r="AI96" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ96" t="s">
         <v>46</v>
@@ -12276,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="AI97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ97" t="s">
         <v>46</v>
@@ -12387,7 +12397,7 @@
         <v>0</v>
       </c>
       <c r="AI98" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ98" t="s">
         <v>46</v>
@@ -12684,7 +12694,7 @@
         <v>0</v>
       </c>
       <c r="AI101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ101" t="s">
         <v>46</v>
@@ -12795,7 +12805,7 @@
         <v>0</v>
       </c>
       <c r="AI102" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ102" t="s">
         <v>46</v>
@@ -12906,7 +12916,7 @@
         <v>0</v>
       </c>
       <c r="AI103" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ103" t="s">
         <v>46</v>
@@ -13017,7 +13027,7 @@
         <v>0</v>
       </c>
       <c r="AI104" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ104" t="s">
         <v>46</v>
@@ -13128,7 +13138,7 @@
         <v>0</v>
       </c>
       <c r="AI105" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ105" t="s">
         <v>46</v>
@@ -13344,7 +13354,7 @@
         <v>0</v>
       </c>
       <c r="AI107" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ107" t="s">
         <v>46</v>
@@ -13566,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="AI109" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ109" t="s">
         <v>46</v>
@@ -13788,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="AI111" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ111" t="s">
         <v>46</v>
@@ -13899,7 +13909,7 @@
         <v>0</v>
       </c>
       <c r="AI112" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ112" t="s">
         <v>46</v>
@@ -14010,7 +14020,7 @@
         <v>0</v>
       </c>
       <c r="AI113" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ113" t="s">
         <v>46</v>
@@ -14412,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AI117" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ117" t="s">
         <v>46</v>
@@ -14634,7 +14644,7 @@
         <v>0</v>
       </c>
       <c r="AI119" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ119" t="s">
         <v>46</v>
@@ -14745,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="AI120" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ120" t="s">
         <v>46</v>
@@ -14856,7 +14866,7 @@
         <v>0</v>
       </c>
       <c r="AI121" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ121" t="s">
         <v>46</v>
@@ -14967,7 +14977,7 @@
         <v>0</v>
       </c>
       <c r="AI122" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ122" t="s">
         <v>46</v>
@@ -15393,7 +15403,7 @@
         <v>1</v>
       </c>
       <c r="AI126" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ126" t="s">
         <v>46</v>
@@ -15504,7 +15514,7 @@
         <v>1</v>
       </c>
       <c r="AI127" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ127" t="s">
         <v>46</v>
@@ -15615,7 +15625,7 @@
         <v>0</v>
       </c>
       <c r="AI128" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ128" t="s">
         <v>46</v>
@@ -15726,7 +15736,7 @@
         <v>0</v>
       </c>
       <c r="AI129" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ129" t="s">
         <v>46</v>
@@ -15837,7 +15847,7 @@
         <v>0</v>
       </c>
       <c r="AI130" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ130" t="s">
         <v>46</v>
@@ -15948,7 +15958,7 @@
         <v>0</v>
       </c>
       <c r="AI131" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ131" t="s">
         <v>46</v>
@@ -16059,7 +16069,7 @@
         <v>0</v>
       </c>
       <c r="AI132" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ132" t="s">
         <v>46</v>
@@ -16170,7 +16180,7 @@
         <v>0</v>
       </c>
       <c r="AI133" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ133" t="s">
         <v>46</v>
@@ -16281,7 +16291,7 @@
         <v>0</v>
       </c>
       <c r="AI134" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ134" t="s">
         <v>46</v>
@@ -16503,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="AI136" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ136" t="s">
         <v>46</v>
@@ -16614,7 +16624,7 @@
         <v>0</v>
       </c>
       <c r="AI137" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ137" t="s">
         <v>46</v>
@@ -16812,7 +16822,7 @@
         <v>0</v>
       </c>
       <c r="AI139" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ139" t="s">
         <v>46</v>
@@ -16923,7 +16933,7 @@
         <v>0</v>
       </c>
       <c r="AI140" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ140" t="s">
         <v>46</v>
@@ -17034,7 +17044,7 @@
         <v>0</v>
       </c>
       <c r="AI141" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ141" t="s">
         <v>46</v>
@@ -17145,7 +17155,7 @@
         <v>0</v>
       </c>
       <c r="AI142" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ142" t="s">
         <v>46</v>
@@ -17256,7 +17266,7 @@
         <v>0</v>
       </c>
       <c r="AI143" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ143" t="s">
         <v>46</v>
@@ -17367,7 +17377,7 @@
         <v>0</v>
       </c>
       <c r="AI144" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ144" t="s">
         <v>46</v>
@@ -17478,7 +17488,7 @@
         <v>0</v>
       </c>
       <c r="AI145" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ145" t="s">
         <v>46</v>
@@ -17589,7 +17599,7 @@
         <v>0</v>
       </c>
       <c r="AI146" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ146" t="s">
         <v>46</v>
@@ -17700,7 +17710,7 @@
         <v>0</v>
       </c>
       <c r="AI147" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ147" t="s">
         <v>46</v>
@@ -17811,7 +17821,7 @@
         <v>0</v>
       </c>
       <c r="AI148" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ148" t="s">
         <v>46</v>
@@ -17922,7 +17932,7 @@
         <v>0</v>
       </c>
       <c r="AI149" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ149" t="s">
         <v>46</v>
@@ -18144,7 +18154,7 @@
         <v>0</v>
       </c>
       <c r="AI151" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ151" t="s">
         <v>46</v>
@@ -18477,7 +18487,7 @@
         <v>0</v>
       </c>
       <c r="AI154" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ154" t="s">
         <v>46</v>
@@ -18582,7 +18592,7 @@
         <v>0</v>
       </c>
       <c r="AI155" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ155" t="s">
         <v>46</v>
@@ -18786,7 +18796,7 @@
         <v>0</v>
       </c>
       <c r="AI157" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ157" t="s">
         <v>46</v>
@@ -18897,7 +18907,7 @@
         <v>0</v>
       </c>
       <c r="AI158" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ158" t="s">
         <v>46</v>
@@ -19008,7 +19018,7 @@
         <v>0</v>
       </c>
       <c r="AI159" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ159" t="s">
         <v>46</v>
@@ -19119,7 +19129,7 @@
         <v>0</v>
       </c>
       <c r="AI160" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ160" t="s">
         <v>46</v>
@@ -19230,7 +19240,7 @@
         <v>0</v>
       </c>
       <c r="AI161" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ161" t="s">
         <v>46</v>
@@ -19341,7 +19351,7 @@
         <v>0</v>
       </c>
       <c r="AI162" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ162" t="s">
         <v>46</v>
@@ -19545,7 +19555,7 @@
         <v>0</v>
       </c>
       <c r="AI164" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ164" t="s">
         <v>46</v>
@@ -19656,7 +19666,7 @@
         <v>0</v>
       </c>
       <c r="AI165" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ165" t="s">
         <v>46</v>
@@ -19767,7 +19777,7 @@
         <v>0</v>
       </c>
       <c r="AI166" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ166" t="s">
         <v>46</v>
@@ -20100,7 +20110,7 @@
         <v>0</v>
       </c>
       <c r="AI169" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ169" t="s">
         <v>46</v>
@@ -20211,7 +20221,7 @@
         <v>0</v>
       </c>
       <c r="AI170" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ170" t="s">
         <v>46</v>
@@ -20322,7 +20332,7 @@
         <v>0</v>
       </c>
       <c r="AI171" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ171" t="s">
         <v>46</v>
@@ -20823,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="AI176" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ176" t="s">
         <v>46</v>
@@ -21366,7 +21376,7 @@
         <v>0</v>
       </c>
       <c r="AI181" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ181" t="s">
         <v>46</v>
@@ -21849,7 +21859,7 @@
         <v>0</v>
       </c>
       <c r="AI186" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ186" t="s">
         <v>46</v>
@@ -22071,7 +22081,7 @@
         <v>0</v>
       </c>
       <c r="AI188" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ188" t="s">
         <v>46</v>
@@ -22275,7 +22285,7 @@
         <v>0</v>
       </c>
       <c r="AI190" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ190" t="s">
         <v>46</v>
@@ -22487,7 +22497,7 @@
         <v>0</v>
       </c>
       <c r="AI192" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ192" t="s">
         <v>46</v>
@@ -22598,7 +22608,7 @@
         <v>0</v>
       </c>
       <c r="AI193" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ193" t="s">
         <v>46</v>
@@ -22709,7 +22719,7 @@
         <v>0</v>
       </c>
       <c r="AI194" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ194" t="s">
         <v>46</v>
@@ -22820,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="AI195" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ195" t="s">
         <v>46</v>
@@ -23141,7 +23151,7 @@
         <v>0</v>
       </c>
       <c r="AI198" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ198" t="s">
         <v>46</v>
@@ -23246,7 +23256,7 @@
         <v>0</v>
       </c>
       <c r="AI199" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ199" t="s">
         <v>46</v>
@@ -23351,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="AI200" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ200" t="s">
         <v>46</v>
@@ -23676,7 +23686,7 @@
         <v>0</v>
       </c>
       <c r="AI203" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ203" t="s">
         <v>46</v>
@@ -23787,7 +23797,7 @@
         <v>0</v>
       </c>
       <c r="AI204" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ204" t="s">
         <v>46</v>
@@ -23898,7 +23908,7 @@
         <v>0</v>
       </c>
       <c r="AI205" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ205" t="s">
         <v>46</v>
@@ -24003,7 +24013,7 @@
         <v>0</v>
       </c>
       <c r="AI206" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ206" t="s">
         <v>46</v>
@@ -24114,7 +24124,7 @@
         <v>0</v>
       </c>
       <c r="AI207" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ207" t="s">
         <v>46</v>
@@ -24225,7 +24235,7 @@
         <v>0</v>
       </c>
       <c r="AI208" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ208" t="s">
         <v>46</v>
@@ -24336,7 +24346,7 @@
         <v>0</v>
       </c>
       <c r="AI209" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ209" t="s">
         <v>46</v>
@@ -24441,7 +24451,7 @@
         <v>0</v>
       </c>
       <c r="AI210" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ210" t="s">
         <v>46</v>
@@ -24552,7 +24562,7 @@
         <v>0</v>
       </c>
       <c r="AI211" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ211" t="s">
         <v>46</v>
@@ -24663,7 +24673,7 @@
         <v>0</v>
       </c>
       <c r="AI212" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ212" t="s">
         <v>46</v>
@@ -25065,7 +25075,7 @@
         <v>0</v>
       </c>
       <c r="AI216" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ216" t="s">
         <v>46</v>
@@ -25176,7 +25186,7 @@
         <v>0</v>
       </c>
       <c r="AI217" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ217" t="s">
         <v>46</v>
@@ -25287,7 +25297,7 @@
         <v>0</v>
       </c>
       <c r="AI218" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ218" t="s">
         <v>46</v>
@@ -25398,7 +25408,7 @@
         <v>0</v>
       </c>
       <c r="AI219" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ219" t="s">
         <v>46</v>
@@ -25509,7 +25519,7 @@
         <v>0</v>
       </c>
       <c r="AI220" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ220" t="s">
         <v>46</v>
@@ -25935,7 +25945,7 @@
         <v>0</v>
       </c>
       <c r="AI224" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ224" t="s">
         <v>46</v>
@@ -26046,7 +26056,7 @@
         <v>0</v>
       </c>
       <c r="AI225" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ225" t="s">
         <v>46</v>
@@ -26258,7 +26268,7 @@
         <v>0</v>
       </c>
       <c r="AI227" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ227" t="s">
         <v>46</v>
@@ -26369,7 +26379,7 @@
         <v>0</v>
       </c>
       <c r="AI228" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ228" t="s">
         <v>46</v>
@@ -26573,7 +26583,7 @@
         <v>0</v>
       </c>
       <c r="AI230" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ230" t="s">
         <v>46</v>
@@ -26795,7 +26805,7 @@
         <v>0</v>
       </c>
       <c r="AI232" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ232" t="s">
         <v>46</v>
@@ -26906,7 +26916,7 @@
         <v>0</v>
       </c>
       <c r="AI233" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ233" t="s">
         <v>46</v>
@@ -27011,7 +27021,7 @@
         <v>0</v>
       </c>
       <c r="AI234" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ234" t="s">
         <v>46</v>
@@ -27122,7 +27132,7 @@
         <v>0</v>
       </c>
       <c r="AI235" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ235" t="s">
         <v>46</v>
@@ -27233,7 +27243,7 @@
         <v>0</v>
       </c>
       <c r="AI236" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ236" t="s">
         <v>46</v>
@@ -27455,7 +27465,7 @@
         <v>0</v>
       </c>
       <c r="AI238" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ238" t="s">
         <v>46</v>
@@ -27566,7 +27576,7 @@
         <v>0</v>
       </c>
       <c r="AI239" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ239" t="s">
         <v>46</v>
@@ -27677,7 +27687,7 @@
         <v>0</v>
       </c>
       <c r="AI240" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ240" t="s">
         <v>46</v>
@@ -27899,7 +27909,7 @@
         <v>0</v>
       </c>
       <c r="AI242" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ242" t="s">
         <v>46</v>
@@ -28010,7 +28020,7 @@
         <v>0</v>
       </c>
       <c r="AI243" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ243" t="s">
         <v>46</v>
@@ -28232,7 +28242,7 @@
         <v>0</v>
       </c>
       <c r="AI245" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ245" t="s">
         <v>46</v>
@@ -28634,7 +28644,7 @@
         <v>0</v>
       </c>
       <c r="AI249" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ249" t="s">
         <v>46</v>
@@ -28856,7 +28866,7 @@
         <v>0</v>
       </c>
       <c r="AI251" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ251" t="s">
         <v>46</v>
@@ -28967,7 +28977,7 @@
         <v>0</v>
       </c>
       <c r="AI252" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ252" t="s">
         <v>46</v>
@@ -29078,7 +29088,7 @@
         <v>0</v>
       </c>
       <c r="AI253" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ253" t="s">
         <v>46</v>
@@ -29300,7 +29310,7 @@
         <v>0</v>
       </c>
       <c r="AI255" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ255" t="s">
         <v>46</v>
@@ -29405,7 +29415,7 @@
         <v>0</v>
       </c>
       <c r="AI256" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ256" t="s">
         <v>46</v>
@@ -29516,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="AI257" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ257" t="s">
         <v>46</v>
@@ -29627,7 +29637,7 @@
         <v>0</v>
       </c>
       <c r="AI258" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ258" t="s">
         <v>46</v>
@@ -29738,7 +29748,7 @@
         <v>0</v>
       </c>
       <c r="AI259" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ259" t="s">
         <v>46</v>
@@ -29849,7 +29859,7 @@
         <v>0</v>
       </c>
       <c r="AI260" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AJ260" t="s">
         <v>46</v>
